--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="582" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51C3C5EC-2F14-4530-8072-BA87447F3FFB}"/>
+  <xr:revisionPtr revIDLastSave="586" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D9C0FF4-461E-4569-B067-D62AB596880B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="430">
   <si>
     <t>Col 1</t>
   </si>
@@ -1325,6 +1325,9 @@
   </si>
   <si>
     <t>se agrega 0256</t>
+  </si>
+  <si>
+    <t>59Z176-C01-A*</t>
   </si>
 </sst>
 </file>
@@ -6821,7 +6824,7 @@
         <v>54</v>
       </c>
       <c r="I3" s="36" t="s">
-        <v>7</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:101" x14ac:dyDescent="0.35">
@@ -7310,14 +7313,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="51" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="52" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7427,7 +7430,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>426</v>
       </c>
@@ -7475,7 +7478,7 @@
       <c r="AI2" s="39"/>
       <c r="AJ2" s="39"/>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>262</v>
       </c>
@@ -7582,7 +7585,7 @@
         <v>2098700189</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>310</v>
       </c>
@@ -7638,7 +7641,7 @@
         <v>2154150715</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>312</v>
       </c>
@@ -7703,7 +7706,7 @@
         <v>2098706010</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>314</v>
       </c>
@@ -7792,7 +7795,7 @@
         <v>2088702198</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>316</v>
       </c>
@@ -7946,8 +7949,11 @@
       <c r="AY7" s="36">
         <v>2098700433</v>
       </c>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.35">
+      <c r="AZ7" s="36">
+        <v>2088701390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>318</v>
       </c>
@@ -8027,7 +8033,7 @@
         <v>2088707042</v>
       </c>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>320</v>
       </c>
@@ -8071,7 +8077,7 @@
         <v>2098700437</v>
       </c>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>322</v>
       </c>
@@ -8097,7 +8103,7 @@
         <v>2154170049</v>
       </c>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>324</v>
       </c>

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="586" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D9C0FF4-461E-4569-B067-D62AB596880B}"/>
+  <xr:revisionPtr revIDLastSave="628" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1137C30D-40AF-40EE-A53C-D4B86EA97D75}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="430">
   <si>
     <t>Col 1</t>
   </si>
@@ -1327,14 +1327,14 @@
     <t>se agrega 0256</t>
   </si>
   <si>
-    <t>59Z176-C01-A*</t>
+    <t>AMZ025-000-F</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1374,8 +1374,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1428,6 +1434,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="mediumGray">
+        <fgColor indexed="9"/>
+        <bgColor indexed="43"/>
       </patternFill>
     </fill>
   </fills>
@@ -1678,7 +1690,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1757,6 +1769,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2713,19 +2729,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H233"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
@@ -2751,7 +2767,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>2088701244</v>
       </c>
@@ -2765,7 +2781,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2088701390</v>
       </c>
@@ -2779,7 +2795,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>2088701610</v>
       </c>
@@ -2793,7 +2809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>2088701746</v>
       </c>
@@ -2804,7 +2820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>2088702198</v>
       </c>
@@ -2818,7 +2834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>2088702199</v>
       </c>
@@ -2832,7 +2848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>2088702200</v>
       </c>
@@ -2846,7 +2862,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>2088702201</v>
       </c>
@@ -2863,7 +2879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>2088702202</v>
       </c>
@@ -2877,7 +2893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>2088702203</v>
       </c>
@@ -2891,7 +2907,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>2088702204</v>
       </c>
@@ -2905,7 +2921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>2088702205</v>
       </c>
@@ -2919,7 +2935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>2088702206</v>
       </c>
@@ -2933,7 +2949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>2088702207</v>
       </c>
@@ -2959,7 +2975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>2088702221</v>
       </c>
@@ -2973,7 +2989,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>2088702318</v>
       </c>
@@ -2987,7 +3003,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>2088707042</v>
       </c>
@@ -3001,7 +3017,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>2098700024</v>
       </c>
@@ -3015,7 +3031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4">
       <c r="A20" s="5">
         <v>2098700025</v>
       </c>
@@ -3029,7 +3045,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>2098700026</v>
       </c>
@@ -3043,7 +3059,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>2098700033</v>
       </c>
@@ -3057,7 +3073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>2098700046</v>
       </c>
@@ -3071,7 +3087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>2098700056</v>
       </c>
@@ -3085,7 +3101,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>2098700058</v>
       </c>
@@ -3099,7 +3115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>2098700076</v>
       </c>
@@ -3113,7 +3129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>2098700083</v>
       </c>
@@ -3127,7 +3143,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4">
       <c r="A28" s="5">
         <v>2098700108</v>
       </c>
@@ -3141,7 +3157,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>2098700143</v>
       </c>
@@ -3155,7 +3171,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>2098700154</v>
       </c>
@@ -3169,7 +3185,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>2098700177</v>
       </c>
@@ -3183,7 +3199,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>2098700189</v>
       </c>
@@ -3197,7 +3213,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>2098700245</v>
       </c>
@@ -3211,7 +3227,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34" s="5">
         <v>2098700246</v>
       </c>
@@ -3225,7 +3241,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35" s="5">
         <v>2098700256</v>
       </c>
@@ -3239,7 +3255,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>2098700289</v>
       </c>
@@ -3253,7 +3269,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>2098700290</v>
       </c>
@@ -3267,7 +3283,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>2098700293</v>
       </c>
@@ -3281,7 +3297,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>2098700296</v>
       </c>
@@ -3298,7 +3314,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>2098700301</v>
       </c>
@@ -3312,7 +3328,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>2098700302</v>
       </c>
@@ -3326,7 +3342,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>2098700304</v>
       </c>
@@ -3340,7 +3356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>2098700305</v>
       </c>
@@ -3354,7 +3370,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>2098700306</v>
       </c>
@@ -3368,7 +3384,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>2098700307</v>
       </c>
@@ -3382,7 +3398,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>2098700309</v>
       </c>
@@ -3396,7 +3412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>2098700315</v>
       </c>
@@ -3410,7 +3426,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>2098700316</v>
       </c>
@@ -3424,7 +3440,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4">
       <c r="A49">
         <v>2098700320</v>
       </c>
@@ -3438,7 +3454,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4">
       <c r="A50">
         <v>2098700322</v>
       </c>
@@ -3452,7 +3468,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4">
       <c r="A51">
         <v>2098700353</v>
       </c>
@@ -3466,7 +3482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4">
       <c r="A52">
         <v>2098700355</v>
       </c>
@@ -3480,7 +3496,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4">
       <c r="A53">
         <v>2098700356</v>
       </c>
@@ -3494,7 +3510,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4">
       <c r="A54">
         <v>2098700357</v>
       </c>
@@ -3508,7 +3524,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4">
       <c r="A55">
         <v>2098700358</v>
       </c>
@@ -3522,7 +3538,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4">
       <c r="A56">
         <v>2098700366</v>
       </c>
@@ -3536,7 +3552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4">
       <c r="A57">
         <v>2098700371</v>
       </c>
@@ -3550,7 +3566,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4">
       <c r="A58">
         <v>2098700372</v>
       </c>
@@ -3564,7 +3580,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4">
       <c r="A59">
         <v>2098700373</v>
       </c>
@@ -3578,7 +3594,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4">
       <c r="A60">
         <v>2098700374</v>
       </c>
@@ -3592,7 +3608,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4">
       <c r="A61">
         <v>2098700375</v>
       </c>
@@ -3606,7 +3622,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4">
       <c r="A62">
         <v>2098700376</v>
       </c>
@@ -3620,7 +3636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4">
       <c r="A63">
         <v>2098700378</v>
       </c>
@@ -3634,7 +3650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4">
       <c r="A64" s="5">
         <v>2098700379</v>
       </c>
@@ -3648,7 +3664,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5">
       <c r="A65" s="5">
         <v>2098700380</v>
       </c>
@@ -3662,7 +3678,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5">
       <c r="A66" s="5">
         <v>2098700404</v>
       </c>
@@ -3676,7 +3692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5">
       <c r="A67" s="5">
         <v>2098700405</v>
       </c>
@@ -3690,7 +3706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>2098700429</v>
       </c>
@@ -3704,7 +3720,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5">
       <c r="A69" s="5">
         <v>2098700432</v>
       </c>
@@ -3718,7 +3734,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5">
       <c r="A70" s="5">
         <v>2098700433</v>
       </c>
@@ -3732,7 +3748,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5">
       <c r="A71" s="5">
         <v>2098700434</v>
       </c>
@@ -3746,7 +3762,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5">
       <c r="A72" s="5">
         <v>2098700436</v>
       </c>
@@ -3760,7 +3776,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5">
       <c r="A73" s="5">
         <v>2098700437</v>
       </c>
@@ -3777,7 +3793,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>2098701682</v>
       </c>
@@ -3791,7 +3807,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>2098706005</v>
       </c>
@@ -3805,7 +3821,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5">
       <c r="A76">
         <v>2098706008</v>
       </c>
@@ -3819,7 +3835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>2098706009</v>
       </c>
@@ -3833,7 +3849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5">
       <c r="A78">
         <v>2098706010</v>
       </c>
@@ -3847,7 +3863,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>2098706011</v>
       </c>
@@ -3861,7 +3877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>2098706013</v>
       </c>
@@ -3875,7 +3891,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4">
       <c r="A81">
         <v>2098706018</v>
       </c>
@@ -3889,7 +3905,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4">
       <c r="A82">
         <v>2098706021</v>
       </c>
@@ -3903,7 +3919,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4">
       <c r="A83">
         <v>2098706023</v>
       </c>
@@ -3917,7 +3933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4">
       <c r="A84">
         <v>2098706024</v>
       </c>
@@ -3931,7 +3947,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4">
       <c r="A85">
         <v>2098706025</v>
       </c>
@@ -3945,7 +3961,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4">
       <c r="A86">
         <v>2098706026</v>
       </c>
@@ -3959,7 +3975,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4">
       <c r="A87">
         <v>2098706028</v>
       </c>
@@ -3973,7 +3989,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4">
       <c r="A88">
         <v>2098706031</v>
       </c>
@@ -3987,7 +4003,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4">
       <c r="A89">
         <v>2098706032</v>
       </c>
@@ -4001,7 +4017,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4">
       <c r="A90">
         <v>2098706040</v>
       </c>
@@ -4015,7 +4031,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4">
       <c r="A91">
         <v>2098706041</v>
       </c>
@@ -4029,7 +4045,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4">
       <c r="A92">
         <v>2098706044</v>
       </c>
@@ -4043,7 +4059,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4">
       <c r="A93" s="5">
         <v>2098706072</v>
       </c>
@@ -4057,7 +4073,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4">
       <c r="A94" s="5">
         <v>2098706075</v>
       </c>
@@ -4071,7 +4087,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4">
       <c r="A95" s="5">
         <v>2098706076</v>
       </c>
@@ -4085,7 +4101,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4">
       <c r="A96">
         <v>2098706083</v>
       </c>
@@ -4099,7 +4115,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>2098706084</v>
       </c>
@@ -4113,7 +4129,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>2098706085</v>
       </c>
@@ -4127,7 +4143,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7">
       <c r="A99" s="5">
         <v>2098706087</v>
       </c>
@@ -4141,7 +4157,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7">
       <c r="A100" s="5">
         <v>2098706089</v>
       </c>
@@ -4155,7 +4171,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7">
       <c r="A101" s="5">
         <v>2099700009</v>
       </c>
@@ -4169,7 +4185,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7">
       <c r="A102" s="5">
         <v>2099700010</v>
       </c>
@@ -4183,7 +4199,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>2099700025</v>
       </c>
@@ -4200,7 +4216,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>2099700030</v>
       </c>
@@ -4220,7 +4236,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7">
       <c r="A105" s="5">
         <v>2099700041</v>
       </c>
@@ -4234,7 +4250,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>2099700048</v>
       </c>
@@ -4248,7 +4264,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7">
       <c r="A107" s="5">
         <v>2099700049</v>
       </c>
@@ -4262,7 +4278,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7">
       <c r="A108" s="5">
         <v>2099700056</v>
       </c>
@@ -4276,7 +4292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7">
       <c r="A109" s="5">
         <v>2099700057</v>
       </c>
@@ -4293,7 +4309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7">
       <c r="A110" s="5">
         <v>2099700058</v>
       </c>
@@ -4316,7 +4332,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7">
       <c r="A111" s="5">
         <v>2099700059</v>
       </c>
@@ -4339,7 +4355,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7">
       <c r="A112" s="5">
         <v>2099706005</v>
       </c>
@@ -4353,7 +4369,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4">
       <c r="A113" s="5">
         <v>2154140069</v>
       </c>
@@ -4367,7 +4383,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4">
       <c r="A114" s="5">
         <v>2154140162</v>
       </c>
@@ -4381,7 +4397,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4">
       <c r="A115" s="5">
         <v>2154140207</v>
       </c>
@@ -4395,7 +4411,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4">
       <c r="A116">
         <v>2154140222</v>
       </c>
@@ -4409,7 +4425,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4">
       <c r="A117">
         <v>2154140224</v>
       </c>
@@ -4423,7 +4439,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4">
       <c r="A118">
         <v>2154140225</v>
       </c>
@@ -4437,7 +4453,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4">
       <c r="A119">
         <v>2154140229</v>
       </c>
@@ -4451,7 +4467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4">
       <c r="A120">
         <v>2154140243</v>
       </c>
@@ -4465,7 +4481,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4">
       <c r="A121">
         <v>2154140283</v>
       </c>
@@ -4479,7 +4495,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4">
       <c r="A122">
         <v>2154140284</v>
       </c>
@@ -4493,7 +4509,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4">
       <c r="A123" s="5">
         <v>2154140285</v>
       </c>
@@ -4507,7 +4523,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4">
       <c r="A124">
         <v>2154140287</v>
       </c>
@@ -4521,7 +4537,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4">
       <c r="A125">
         <v>2154140289</v>
       </c>
@@ -4535,7 +4551,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4">
       <c r="A126">
         <v>2154140290</v>
       </c>
@@ -4549,7 +4565,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4">
       <c r="A127" s="5">
         <v>2154140291</v>
       </c>
@@ -4563,7 +4579,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4">
       <c r="A128" s="5">
         <v>2154140292</v>
       </c>
@@ -4577,7 +4593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4">
       <c r="A129">
         <v>2154140293</v>
       </c>
@@ -4591,7 +4607,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4">
       <c r="A130">
         <v>2154140294</v>
       </c>
@@ -4605,7 +4621,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4">
       <c r="A131">
         <v>2154140295</v>
       </c>
@@ -4619,7 +4635,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4">
       <c r="A132">
         <v>2154140318</v>
       </c>
@@ -4633,7 +4649,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4">
       <c r="A133">
         <v>2154140319</v>
       </c>
@@ -4647,7 +4663,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4">
       <c r="A134" s="5">
         <v>2154140335</v>
       </c>
@@ -4661,7 +4677,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4">
       <c r="A135">
         <v>2154140336</v>
       </c>
@@ -4675,7 +4691,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4">
       <c r="A136" s="5">
         <v>2154140345</v>
       </c>
@@ -4689,7 +4705,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4">
       <c r="A137">
         <v>2154140349</v>
       </c>
@@ -4703,7 +4719,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4">
       <c r="A138" s="5">
         <v>2154140596</v>
       </c>
@@ -4717,7 +4733,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4">
       <c r="A139">
         <v>2154150035</v>
       </c>
@@ -4731,7 +4747,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4">
       <c r="A140">
         <v>2154150089</v>
       </c>
@@ -4745,7 +4761,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4">
       <c r="A141">
         <v>2154150163</v>
       </c>
@@ -4759,7 +4775,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4">
       <c r="A142">
         <v>2154150172</v>
       </c>
@@ -4773,7 +4789,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4">
       <c r="A143">
         <v>2154150197</v>
       </c>
@@ -4787,7 +4803,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4">
       <c r="A144">
         <v>2154150214</v>
       </c>
@@ -4801,7 +4817,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5">
       <c r="A145">
         <v>2154150215</v>
       </c>
@@ -4815,7 +4831,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5">
       <c r="A146">
         <v>2154150247</v>
       </c>
@@ -4829,7 +4845,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5">
       <c r="A147">
         <v>2154150250</v>
       </c>
@@ -4843,7 +4859,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5">
       <c r="A148" s="5">
         <v>2154150301</v>
       </c>
@@ -4857,7 +4873,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5">
       <c r="A149">
         <v>2154150337</v>
       </c>
@@ -4871,7 +4887,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5">
       <c r="A150">
         <v>2154150341</v>
       </c>
@@ -4885,7 +4901,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5">
       <c r="A151">
         <v>2154150342</v>
       </c>
@@ -4899,7 +4915,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5">
       <c r="A152" s="5">
         <v>2154150343</v>
       </c>
@@ -4913,7 +4929,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5">
       <c r="A153" s="5">
         <v>2154150347</v>
       </c>
@@ -4927,7 +4943,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5">
       <c r="A154">
         <v>2154150348</v>
       </c>
@@ -4941,7 +4957,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5">
       <c r="A155" s="5">
         <v>2154150349</v>
       </c>
@@ -4955,7 +4971,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5">
       <c r="A156" s="5">
         <v>2154150350</v>
       </c>
@@ -4972,7 +4988,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5">
       <c r="A157" s="5">
         <v>2154150351</v>
       </c>
@@ -4986,7 +5002,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5">
       <c r="A158" s="5">
         <v>2154150357</v>
       </c>
@@ -5003,7 +5019,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5">
       <c r="A159" s="5">
         <v>2154150358</v>
       </c>
@@ -5017,7 +5033,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5">
       <c r="A160" s="5">
         <v>2154150366</v>
       </c>
@@ -5034,7 +5050,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5">
       <c r="A161" s="5">
         <v>2154150370</v>
       </c>
@@ -5048,7 +5064,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5">
       <c r="A162">
         <v>2154150380</v>
       </c>
@@ -5062,7 +5078,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5">
       <c r="A163">
         <v>2154150391</v>
       </c>
@@ -5076,7 +5092,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5">
       <c r="A164">
         <v>2154150420</v>
       </c>
@@ -5090,7 +5106,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5">
       <c r="A165">
         <v>2154150447</v>
       </c>
@@ -5104,7 +5120,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5">
       <c r="A166" s="5">
         <v>2154150448</v>
       </c>
@@ -5118,7 +5134,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5">
       <c r="A167" s="5">
         <v>2154150455</v>
       </c>
@@ -5135,7 +5151,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5">
       <c r="A168">
         <v>2154150461</v>
       </c>
@@ -5149,7 +5165,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5">
       <c r="A169" s="5">
         <v>2154150497</v>
       </c>
@@ -5163,7 +5179,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5">
       <c r="A170" s="5">
         <v>2154150501</v>
       </c>
@@ -5177,7 +5193,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5">
       <c r="A171" s="5">
         <v>2154150509</v>
       </c>
@@ -5191,7 +5207,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5">
       <c r="A172" s="5">
         <v>2154150525</v>
       </c>
@@ -5208,7 +5224,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5">
       <c r="A173" s="5">
         <v>2154150526</v>
       </c>
@@ -5222,7 +5238,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5">
       <c r="A174" s="5">
         <v>2154150534</v>
       </c>
@@ -5239,7 +5255,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5">
       <c r="A175">
         <v>2154150554</v>
       </c>
@@ -5253,7 +5269,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5">
       <c r="A176" s="5">
         <v>2154150557</v>
       </c>
@@ -5267,7 +5283,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6">
       <c r="A177" s="5">
         <v>2154150560</v>
       </c>
@@ -5287,7 +5303,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6">
       <c r="A178">
         <v>2154150563</v>
       </c>
@@ -5301,7 +5317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6">
       <c r="A179" s="5">
         <v>2154150581</v>
       </c>
@@ -5315,7 +5331,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6">
       <c r="A180">
         <v>2154150582</v>
       </c>
@@ -5329,7 +5345,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6">
       <c r="A181">
         <v>2154150588</v>
       </c>
@@ -5343,7 +5359,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6">
       <c r="A182" s="5">
         <v>2154150591</v>
       </c>
@@ -5360,7 +5376,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6">
       <c r="A183" s="5">
         <v>2154150597</v>
       </c>
@@ -5377,7 +5393,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6">
       <c r="A184">
         <v>2154150603</v>
       </c>
@@ -5391,7 +5407,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6">
       <c r="A185">
         <v>2154150605</v>
       </c>
@@ -5405,7 +5421,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6">
       <c r="A186" s="5">
         <v>2154150622</v>
       </c>
@@ -5419,7 +5435,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6">
       <c r="A187" s="5">
         <v>2154150627</v>
       </c>
@@ -5433,7 +5449,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6">
       <c r="A188">
         <v>2154150633</v>
       </c>
@@ -5447,7 +5463,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6">
       <c r="A189" s="5">
         <v>2154150646</v>
       </c>
@@ -5467,7 +5483,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6">
       <c r="A190" s="5">
         <v>2154150648</v>
       </c>
@@ -5487,7 +5503,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6">
       <c r="A191" s="5">
         <v>2154150653</v>
       </c>
@@ -5501,7 +5517,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6">
       <c r="A192">
         <v>2154150669</v>
       </c>
@@ -5515,7 +5531,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6">
       <c r="A193">
         <v>2154150672</v>
       </c>
@@ -5529,7 +5545,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6">
       <c r="A194" s="5">
         <v>2154150677</v>
       </c>
@@ -5546,7 +5562,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6">
       <c r="A195">
         <v>2154150706</v>
       </c>
@@ -5560,7 +5576,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6">
       <c r="A196">
         <v>2154150707</v>
       </c>
@@ -5574,7 +5590,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6">
       <c r="A197">
         <v>2154150715</v>
       </c>
@@ -5588,7 +5604,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6">
       <c r="A198" s="5">
         <v>2154150719</v>
       </c>
@@ -5602,7 +5618,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6">
       <c r="A199" s="5">
         <v>2154150731</v>
       </c>
@@ -5616,7 +5632,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6">
       <c r="A200" s="5">
         <v>2154150765</v>
       </c>
@@ -5636,7 +5652,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6">
       <c r="A201" s="5">
         <v>2154150767</v>
       </c>
@@ -5656,7 +5672,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6">
       <c r="A202" s="5">
         <v>2154150769</v>
       </c>
@@ -5673,7 +5689,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6">
       <c r="A203" s="5">
         <v>2154150788</v>
       </c>
@@ -5687,7 +5703,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6">
       <c r="A204" s="5">
         <v>2154150813</v>
       </c>
@@ -5707,7 +5723,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6">
       <c r="A205" s="5">
         <v>2154150814</v>
       </c>
@@ -5724,7 +5740,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6">
       <c r="A206" s="5">
         <v>2154150822</v>
       </c>
@@ -5741,7 +5757,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6">
       <c r="A207" s="5">
         <v>2154150839</v>
       </c>
@@ -5755,7 +5771,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6">
       <c r="A208" s="5">
         <v>2154150840</v>
       </c>
@@ -5769,7 +5785,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5">
       <c r="A209" s="5">
         <v>2154150841</v>
       </c>
@@ -5783,7 +5799,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5">
       <c r="A210" s="5">
         <v>2154150876</v>
       </c>
@@ -5797,7 +5813,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5">
       <c r="A211" s="5">
         <v>2154150893</v>
       </c>
@@ -5811,7 +5827,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5">
       <c r="A212" s="5">
         <v>2154150918</v>
       </c>
@@ -5825,7 +5841,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5">
       <c r="A213" s="5">
         <v>2154150921</v>
       </c>
@@ -5839,7 +5855,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5">
       <c r="A214" s="5">
         <v>2154150922</v>
       </c>
@@ -5853,7 +5869,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5">
       <c r="A215">
         <v>2154150943</v>
       </c>
@@ -5867,7 +5883,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5">
       <c r="A216">
         <v>2154155136</v>
       </c>
@@ -5881,7 +5897,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5">
       <c r="A217" s="5">
         <v>2154155149</v>
       </c>
@@ -5895,7 +5911,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5">
       <c r="A218" s="5">
         <v>2154155150</v>
       </c>
@@ -5912,7 +5928,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5">
       <c r="A219">
         <v>2154160029</v>
       </c>
@@ -5926,7 +5942,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5">
       <c r="A220">
         <v>2154160030</v>
       </c>
@@ -5940,7 +5956,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5">
       <c r="A221">
         <v>2154160031</v>
       </c>
@@ -5954,7 +5970,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5">
       <c r="A222">
         <v>2154160032</v>
       </c>
@@ -5968,7 +5984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5">
       <c r="A223">
         <v>2154160033</v>
       </c>
@@ -5982,7 +5998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5">
       <c r="A224">
         <v>2154160034</v>
       </c>
@@ -5996,7 +6012,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7">
       <c r="A225">
         <v>2154160035</v>
       </c>
@@ -6010,7 +6026,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7">
       <c r="A226" s="5">
         <v>2154160036</v>
       </c>
@@ -6024,7 +6040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7">
       <c r="A227">
         <v>2154160037</v>
       </c>
@@ -6038,7 +6054,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7">
       <c r="A228">
         <v>2154170049</v>
       </c>
@@ -6052,7 +6068,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7">
       <c r="A229">
         <v>2154170050</v>
       </c>
@@ -6075,7 +6091,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7">
       <c r="A230">
         <v>2154170052</v>
       </c>
@@ -6089,7 +6105,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
     </row>
@@ -6109,86 +6125,101 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CW10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="51" max="52" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="59" max="60" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="61" max="62" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="63" max="64" width="12" bestFit="1" customWidth="1"/>
-    <col min="65" max="66" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="73" max="74" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="75" max="76" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="77" max="78" width="12" bestFit="1" customWidth="1"/>
-    <col min="79" max="80" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="12" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="87" max="88" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="89" max="90" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="91" max="92" width="12" bestFit="1" customWidth="1"/>
-    <col min="93" max="94" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="12" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="12" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="75" max="76" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="12" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="89" max="90" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="12" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:101" ht="15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -6493,7 +6524,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="2" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:101">
       <c r="A2" t="s">
         <v>262</v>
       </c>
@@ -6798,7 +6829,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="3" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:101">
       <c r="A3" t="s">
         <v>310</v>
       </c>
@@ -6806,28 +6837,34 @@
         <v>311</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>52</v>
+        <v>402</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F3" s="36" t="s">
         <v>112</v>
       </c>
       <c r="G3" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="36" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="4" spans="1:101" x14ac:dyDescent="0.35">
+      <c r="K3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:101">
       <c r="A4" t="s">
         <v>312</v>
       </c>
@@ -6838,43 +6875,43 @@
         <v>46</v>
       </c>
       <c r="D4" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="I4" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="J4" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="36" t="s">
+      <c r="M4" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="N4" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="O4" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="M4" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:101" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:101">
       <c r="A5" t="s">
         <v>314</v>
       </c>
@@ -6882,94 +6919,100 @@
         <v>315</v>
       </c>
       <c r="C5" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="J5" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="K5" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="N5" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="P5" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q5" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="R5" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="T5" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="U5" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="V5" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="W5" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="X5" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y5" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z5" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA5" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB5" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC5" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD5" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE5" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>358</v>
+      </c>
+      <c r="AG5" t="s">
         <v>423</v>
       </c>
-      <c r="F5" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="36" t="s">
-        <v>358</v>
-      </c>
-      <c r="I5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="K5" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="L5" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="M5" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="N5" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="P5" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q5" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="S5" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="T5" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="U5" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="V5" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="W5" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="X5" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y5" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z5" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA5" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB5" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="AC5" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD5" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE5" s="37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:101" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:101">
       <c r="A6" t="s">
         <v>316</v>
       </c>
@@ -6977,94 +7020,91 @@
         <v>317</v>
       </c>
       <c r="C6" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="E6" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="L6" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="Q6" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="L6" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" s="36" t="s">
+      <c r="R6" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="N6" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="O6" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="P6" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q6" s="36" t="s">
+      <c r="S6" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="U6" s="36" t="s">
         <v>29</v>
-      </c>
-      <c r="R6" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="T6" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="U6" s="36" t="s">
-        <v>82</v>
       </c>
       <c r="V6" s="36" t="s">
         <v>45</v>
       </c>
       <c r="W6" s="36" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="X6" s="36" t="s">
-        <v>12</v>
+        <v>429</v>
       </c>
       <c r="Y6" s="36" t="s">
-        <v>357</v>
+        <v>153</v>
       </c>
       <c r="Z6" s="37" t="s">
-        <v>365</v>
+        <v>142</v>
       </c>
       <c r="AA6" s="37" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="AB6" s="36" t="s">
-        <v>158</v>
+        <v>358</v>
       </c>
       <c r="AC6" s="36" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="AD6" s="37" t="s">
-        <v>358</v>
-      </c>
-      <c r="AE6" s="36" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:101" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:101">
       <c r="A7" t="s">
         <v>318</v>
       </c>
@@ -7132,7 +7172,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="8" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:101">
       <c r="A8" t="s">
         <v>320</v>
       </c>
@@ -7140,64 +7180,60 @@
         <v>321</v>
       </c>
       <c r="C8" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>369</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="J8" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>368</v>
+      </c>
+      <c r="L8" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="36" t="s">
+      <c r="P8" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q8" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="36" t="s">
+      <c r="R8" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="S8" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="N8" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="O8" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="P8" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q8" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="R8" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="S8" s="37" t="s">
-        <v>373</v>
-      </c>
-      <c r="T8" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="U8" s="37" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="9" spans="1:101" x14ac:dyDescent="0.35">
+      <c r="T8" s="37"/>
+      <c r="U8" s="37"/>
+    </row>
+    <row r="9" spans="1:101">
       <c r="A9" t="s">
         <v>322</v>
       </c>
@@ -7205,43 +7241,43 @@
         <v>323</v>
       </c>
       <c r="C9" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="E9" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>165</v>
-      </c>
       <c r="G9" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="J9" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="H9" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="J9" s="36" t="s">
+      <c r="K9" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="K9" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="L9" s="36" t="s">
+      <c r="L9" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="M9" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="M9" s="36" t="s">
+      <c r="N9" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="N9" s="36" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:101" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:101">
       <c r="A10" t="s">
         <v>426</v>
       </c>
@@ -7249,53 +7285,101 @@
         <v>325</v>
       </c>
       <c r="C10" s="36" t="s">
+        <v>365</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>365</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>373</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="O10" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="R10" s="34" t="s">
         <v>360</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="S10" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="34" t="s">
+        <v>414</v>
+      </c>
+      <c r="U10" s="34" t="s">
+        <v>414</v>
+      </c>
+      <c r="V10" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="W10" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="X10" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y10" s="34" t="s">
+        <v>413</v>
+      </c>
+      <c r="Z10" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA10" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB10" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="AC10" s="34" t="s">
         <v>358</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>412</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="34"/>
-      <c r="W10" s="34"/>
-      <c r="X10" s="34"/>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="34"/>
-      <c r="AA10" s="34"/>
-      <c r="AB10" s="34"/>
-      <c r="AC10" s="34"/>
-      <c r="AD10" s="34"/>
-      <c r="AE10" s="34"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="34"/>
-      <c r="AH10" s="34"/>
+      <c r="AD10" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="AE10" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF10" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="AG10" s="34" t="s">
+        <v>361</v>
+      </c>
+      <c r="AH10" s="34" t="s">
+        <v>45</v>
+      </c>
       <c r="AI10" s="34"/>
       <c r="AJ10" s="34"/>
       <c r="AK10" s="34"/>
@@ -7314,13 +7398,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AZ11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="52" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="52" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:52" ht="15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7430,7 +7514,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:52" ht="15">
       <c r="A2" t="s">
         <v>426</v>
       </c>
@@ -7478,7 +7562,7 @@
       <c r="AI2" s="39"/>
       <c r="AJ2" s="39"/>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
         <v>262</v>
       </c>
@@ -7585,7 +7669,7 @@
         <v>2098700189</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
         <v>310</v>
       </c>
@@ -7641,7 +7725,7 @@
         <v>2154150715</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
         <v>312</v>
       </c>
@@ -7706,7 +7790,7 @@
         <v>2098706010</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
         <v>314</v>
       </c>
@@ -7795,7 +7879,7 @@
         <v>2088702198</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
         <v>316</v>
       </c>
@@ -7953,7 +8037,7 @@
         <v>2088701390</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:52">
       <c r="A8" t="s">
         <v>318</v>
       </c>
@@ -8033,7 +8117,7 @@
         <v>2088707042</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:52">
       <c r="A9" t="s">
         <v>320</v>
       </c>
@@ -8077,7 +8161,7 @@
         <v>2098700437</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:52">
       <c r="A10" t="s">
         <v>322</v>
       </c>
@@ -8103,7 +8187,7 @@
         <v>2154170049</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:52">
       <c r="A11" t="s">
         <v>324</v>
       </c>
@@ -8116,12 +8200,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="66.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>342</v>
       </c>
@@ -8129,7 +8213,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>323</v>
       </c>
@@ -8137,7 +8221,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>315</v>
       </c>
@@ -8145,7 +8229,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>319</v>
       </c>
@@ -8153,7 +8237,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>347</v>
       </c>
@@ -8161,7 +8245,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>315</v>
       </c>
@@ -8169,7 +8253,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>350</v>
       </c>
@@ -8177,7 +8261,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>323</v>
       </c>
@@ -8185,7 +8269,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>317</v>
       </c>
@@ -8193,7 +8277,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>315</v>
       </c>
@@ -8201,7 +8285,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>315</v>
       </c>
@@ -8209,7 +8293,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -8217,7 +8301,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>421</v>
       </c>
@@ -8225,7 +8309,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>325</v>
       </c>
@@ -8233,7 +8317,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>317</v>
       </c>
@@ -8248,20 +8332,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA531276-FCFB-48E9-A31C-F81A22563EEA}">
-  <dimension ref="A1:I40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1">
       <c r="A1" s="7" t="s">
         <v>382</v>
       </c>
@@ -8290,7 +8374,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="15.75" thickBot="1">
       <c r="A2" s="10" t="s">
         <v>391</v>
       </c>
@@ -8319,7 +8403,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="40.5">
       <c r="A3" s="13" t="s">
         <v>400</v>
       </c>
@@ -8347,8 +8431,11 @@
       <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="42" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="40.5">
       <c r="A4" s="16" t="s">
         <v>401</v>
       </c>
@@ -8376,8 +8463,11 @@
       <c r="I4" s="18" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="40.5">
       <c r="A5" s="16" t="s">
         <v>403</v>
       </c>
@@ -8405,8 +8495,11 @@
       <c r="I5" s="18" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="42" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60.75">
       <c r="A6" s="16" t="s">
         <v>404</v>
       </c>
@@ -8434,8 +8527,11 @@
       <c r="I6" s="18" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="40.5">
       <c r="A7" s="16" t="s">
         <v>405</v>
       </c>
@@ -8463,8 +8559,11 @@
       <c r="I7" s="18" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" s="42" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="40.5">
       <c r="A8" s="16" t="s">
         <v>406</v>
       </c>
@@ -8492,8 +8591,11 @@
       <c r="I8" s="18" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8" s="42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="40.5">
       <c r="A9" s="16" t="s">
         <v>407</v>
       </c>
@@ -8521,8 +8623,11 @@
       <c r="I9" s="18" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9" s="42" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="40.5">
       <c r="A10" s="16" t="s">
         <v>130</v>
       </c>
@@ -8548,8 +8653,11 @@
       <c r="I10" s="18" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10" s="42" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="40.5">
       <c r="A11" s="21"/>
       <c r="B11" s="20"/>
       <c r="C11" s="17" t="s">
@@ -8573,8 +8681,11 @@
       <c r="I11" s="18" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11" s="42" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="60.75">
       <c r="A12" s="21"/>
       <c r="B12" s="20"/>
       <c r="C12" s="17" t="s">
@@ -8598,8 +8709,11 @@
       <c r="I12" s="18" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12" s="42" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="40.5">
       <c r="A13" s="21"/>
       <c r="B13" s="20"/>
       <c r="C13" s="17" t="s">
@@ -8623,8 +8737,11 @@
       <c r="I13" s="18" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13" s="42" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="40.5">
       <c r="A14" s="21"/>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -8646,8 +8763,11 @@
       <c r="I14" s="18" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14" s="42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="40.5">
       <c r="A15" s="21"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -8667,8 +8787,11 @@
       <c r="I15" s="18" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15" s="42" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="40.5">
       <c r="A16" s="21"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -8688,8 +8811,11 @@
       <c r="I16" s="18" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16" s="42" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="40.5">
       <c r="A17" s="21"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -8709,8 +8835,11 @@
       <c r="I17" s="18" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17" s="42" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="40.5">
       <c r="A18" s="21"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -8730,8 +8859,11 @@
       <c r="I18" s="18" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18" s="42" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="40.5">
       <c r="A19" s="21"/>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -8751,8 +8883,11 @@
       <c r="I19" s="18" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19" s="42" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="60.75">
       <c r="A20" s="21"/>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -8772,8 +8907,11 @@
       <c r="I20" s="18" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J20" s="42" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="60.75">
       <c r="A21" s="21"/>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -8793,8 +8931,11 @@
       <c r="I21" s="23" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J21" s="42" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="60.75">
       <c r="A22" s="21"/>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -8812,8 +8953,11 @@
       <c r="I22" s="23" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22" s="42" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="60.75">
       <c r="A23" s="21"/>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -8831,8 +8975,11 @@
       <c r="I23" s="18" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J23" s="42" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="60.75">
       <c r="A24" s="25"/>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
@@ -8850,8 +8997,11 @@
       <c r="I24" s="28" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J24" s="42" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="60.75">
       <c r="A25" s="25"/>
       <c r="B25" s="26"/>
       <c r="C25" s="26"/>
@@ -8869,8 +9019,11 @@
       <c r="I25" s="30" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J25" s="42" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="40.5">
       <c r="A26" s="25"/>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -8886,8 +9039,11 @@
       <c r="I26" s="18" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J26" s="42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="40.5">
       <c r="A27" s="25"/>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -8903,8 +9059,11 @@
       <c r="I27" s="30" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J27" s="42" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="40.5">
       <c r="A28" s="21"/>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -8918,8 +9077,11 @@
       <c r="I28" s="30" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J28" s="42" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="40.5">
       <c r="A29" s="21"/>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -8933,8 +9095,11 @@
       <c r="I29" s="30" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J29" s="42" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="40.5">
       <c r="A30" s="21"/>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -8948,8 +9113,11 @@
       <c r="I30" s="18" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J30" s="42" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="40.5">
       <c r="A31" s="21"/>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -8963,8 +9131,11 @@
       <c r="I31" s="18" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J31" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="40.5">
       <c r="A32" s="21"/>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -8978,8 +9149,11 @@
       <c r="I32" s="18" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J32" s="42" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="40.5">
       <c r="A33" s="21"/>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -8993,8 +9167,11 @@
       <c r="I33" s="18" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J33" s="42" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="40.5">
       <c r="A34" s="21"/>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -9006,8 +9183,11 @@
       <c r="I34" s="30" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J34" s="42" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="21"/>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
@@ -9020,7 +9200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10">
       <c r="A36" s="21"/>
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
@@ -9033,7 +9213,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10">
       <c r="A37" s="21"/>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -9046,7 +9226,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10">
       <c r="A38" s="21"/>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -9059,7 +9239,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10">
       <c r="A39" s="21"/>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
@@ -9072,7 +9252,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:10" ht="15" thickBot="1">
       <c r="A40" s="31"/>
       <c r="B40" s="32"/>
       <c r="C40" s="32"/>
@@ -9096,19 +9276,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>262</v>
       </c>
@@ -9137,7 +9317,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>263</v>
       </c>
@@ -9166,7 +9346,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -9195,7 +9375,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>264</v>
       </c>
@@ -9224,7 +9404,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -9253,7 +9433,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -9282,7 +9462,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -9311,7 +9491,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -9340,7 +9520,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>265</v>
       </c>
@@ -9369,7 +9549,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>266</v>
       </c>
@@ -9395,7 +9575,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>267</v>
       </c>
@@ -9421,7 +9601,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>268</v>
       </c>
@@ -9447,7 +9627,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>74</v>
       </c>
@@ -9473,7 +9653,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -9496,7 +9676,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>269</v>
       </c>
@@ -9519,7 +9699,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>270</v>
       </c>
@@ -9542,7 +9722,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>271</v>
       </c>
@@ -9562,7 +9742,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>272</v>
       </c>
@@ -9582,7 +9762,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -9602,7 +9782,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -9622,7 +9802,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -9642,7 +9822,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -9662,7 +9842,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>273</v>
       </c>
@@ -9679,7 +9859,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>274</v>
       </c>
@@ -9693,7 +9873,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>275</v>
       </c>
@@ -9707,7 +9887,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>276</v>
       </c>
@@ -9718,7 +9898,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>277</v>
       </c>
@@ -9729,7 +9909,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -9740,7 +9920,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>278</v>
       </c>
@@ -9751,7 +9931,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -9762,7 +9942,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
         <v>271</v>
       </c>
@@ -9773,7 +9953,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
         <v>272</v>
       </c>
@@ -9784,7 +9964,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -9792,7 +9972,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -9800,7 +9980,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -9808,7 +9988,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -9816,7 +9996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>273</v>
       </c>
@@ -9824,7 +10004,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>274</v>
       </c>
@@ -9832,7 +10012,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>275</v>
       </c>
@@ -9840,7 +10020,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
         <v>276</v>
       </c>
@@ -9848,307 +10028,307 @@
         <v>373</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1">
       <c r="A57" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1">
       <c r="A59" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1">
       <c r="A60" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1">
       <c r="A62" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1">
       <c r="A63" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1">
       <c r="A64" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1">
       <c r="A65" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1">
       <c r="A66" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1">
       <c r="A67" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1">
       <c r="A68" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1">
       <c r="A69" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1">
       <c r="A70" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1">
       <c r="A71" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1">
       <c r="A72" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1">
       <c r="A73" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1">
       <c r="A74" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1">
       <c r="A75" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1">
       <c r="A76" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1">
       <c r="A77" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1">
       <c r="A78" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1">
       <c r="A79" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1">
       <c r="A80" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1">
       <c r="A81" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1">
       <c r="A82" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1">
       <c r="A83" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1">
       <c r="A84" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1">
       <c r="A85" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1">
       <c r="A86" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1">
       <c r="A87" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1">
       <c r="A88" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1">
       <c r="A89" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1">
       <c r="A90" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1">
       <c r="A91" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1">
       <c r="A92" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1">
       <c r="A93" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1">
       <c r="A94" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1">
       <c r="A95" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1">
       <c r="A96" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1">
       <c r="A97" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1">
       <c r="A98" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1">
       <c r="A99" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1">
       <c r="A100" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1">
       <c r="A101" t="s">
         <v>375</v>
       </c>

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="628" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1137C30D-40AF-40EE-A53C-D4B86EA97D75}"/>
+  <xr:revisionPtr revIDLastSave="645" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BDF4B9F-A944-4299-B4A4-A175A3495899}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1841" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="430">
   <si>
     <t>Col 1</t>
   </si>
@@ -1309,9 +1309,6 @@
     <t>59Z153-000-D, se retira modulo 27-jun</t>
   </si>
   <si>
-    <t>59Z178-000-F</t>
-  </si>
-  <si>
     <t>AMS18A-102Z5</t>
   </si>
   <si>
@@ -1328,13 +1325,16 @@
   </si>
   <si>
     <t>AMZ025-000-F</t>
+  </si>
+  <si>
+    <t>Col 102</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1381,7 +1381,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1414,25 +1414,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1442,8 +1424,20 @@
         <bgColor indexed="43"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1686,11 +1680,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1701,9 +1713,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1755,29 +1764,788 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="127">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2047,49 +2815,6 @@
         </left>
         <right style="thin">
           <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
         </right>
         <top/>
         <bottom/>
@@ -2251,6 +2976,20 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -2265,147 +3004,148 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="124" dataDxfId="123">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G230">
     <sortCondition ref="A118:A230"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="122"/>
+    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="117"/>
+    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="116"/>
+    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="115"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CW10" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11">
-  <autoFilter ref="A1:CW10" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}"/>
-  <tableColumns count="101">
-    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1"/>
-    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2"/>
-    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3"/>
-    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4"/>
-    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5"/>
-    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6"/>
-    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7"/>
-    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8"/>
-    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9"/>
-    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10"/>
-    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11"/>
-    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12"/>
-    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13"/>
-    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14"/>
-    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15"/>
-    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16"/>
-    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17"/>
-    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18"/>
-    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19"/>
-    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20"/>
-    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21"/>
-    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22"/>
-    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23"/>
-    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24"/>
-    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25"/>
-    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26"/>
-    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27"/>
-    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28"/>
-    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29"/>
-    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30"/>
-    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31"/>
-    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32"/>
-    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33"/>
-    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34"/>
-    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35"/>
-    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36"/>
-    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37"/>
-    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38"/>
-    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39"/>
-    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40"/>
-    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41"/>
-    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42"/>
-    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43"/>
-    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44"/>
-    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45"/>
-    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46"/>
-    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47"/>
-    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48"/>
-    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49"/>
-    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50"/>
-    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51"/>
-    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52"/>
-    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53"/>
-    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54"/>
-    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55"/>
-    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56"/>
-    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57"/>
-    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58"/>
-    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59"/>
-    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60"/>
-    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61"/>
-    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62"/>
-    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63"/>
-    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64"/>
-    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65"/>
-    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66"/>
-    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67"/>
-    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68"/>
-    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69"/>
-    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70"/>
-    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71"/>
-    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72"/>
-    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73"/>
-    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74"/>
-    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75"/>
-    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76"/>
-    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77"/>
-    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78"/>
-    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79"/>
-    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80"/>
-    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81"/>
-    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82"/>
-    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83"/>
-    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84"/>
-    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85"/>
-    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86"/>
-    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87"/>
-    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88"/>
-    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89"/>
-    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90"/>
-    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91"/>
-    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92"/>
-    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93"/>
-    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94"/>
-    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95"/>
-    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96"/>
-    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97"/>
-    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98"/>
-    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99"/>
-    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100"/>
-    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="126" tableBorderDxfId="125">
+  <autoFilter ref="A1:CX10" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}"/>
+  <tableColumns count="102">
+    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="103"/>
+    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="99"/>
+    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="98"/>
+    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="97"/>
+    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="96"/>
+    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="95"/>
+    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="94"/>
+    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="93"/>
+    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="92"/>
+    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="91"/>
+    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="90"/>
+    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="89"/>
+    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="88"/>
+    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="87"/>
+    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="86"/>
+    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="85"/>
+    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="84"/>
+    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="83"/>
+    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="82"/>
+    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="81"/>
+    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="80"/>
+    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="79"/>
+    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="78"/>
+    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="77"/>
+    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="76"/>
+    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="75"/>
+    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="74"/>
+    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="73"/>
+    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="72"/>
+    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="71"/>
+    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="70"/>
+    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="69"/>
+    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="68"/>
+    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="67"/>
+    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="66"/>
+    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="65"/>
+    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="64"/>
+    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="63"/>
+    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="62"/>
+    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="61"/>
+    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="60"/>
+    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="59"/>
+    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="58"/>
+    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="57"/>
+    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="56"/>
+    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="55"/>
+    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="54"/>
+    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="53"/>
+    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="52"/>
+    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="51"/>
+    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="50"/>
+    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="49"/>
+    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="48"/>
+    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="47"/>
+    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="46"/>
+    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="45"/>
+    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="44"/>
+    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="43"/>
+    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="42"/>
+    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="41"/>
+    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="40"/>
+    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="39"/>
+    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="38"/>
+    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="37"/>
+    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="36"/>
+    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="35"/>
+    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="34"/>
+    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="33"/>
+    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="32"/>
+    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="31"/>
+    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="30"/>
+    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="29"/>
+    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="28"/>
+    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="27"/>
+    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="26"/>
+    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="25"/>
+    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="24"/>
+    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="23"/>
+    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="22"/>
+    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="21"/>
+    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="20"/>
+    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="19"/>
+    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="18"/>
+    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="17"/>
+    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="16"/>
+    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="15"/>
+    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="14"/>
+    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="13"/>
+    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="12"/>
+    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="11"/>
+    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="10"/>
+    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="9"/>
+    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="8"/>
+    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="7"/>
+    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="6"/>
+    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="5"/>
+    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="4"/>
+    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="3"/>
+    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{98029534-FC1A-4188-9735-CF68321B5AC3}" name="Tabla3" displayName="Tabla3" ref="A1:I101" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{98029534-FC1A-4188-9735-CF68321B5AC3}" name="Tabla3" displayName="Tabla3" ref="A1:I101" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
   <autoFilter ref="A1:I101" xr:uid="{98029534-FC1A-4188-9735-CF68321B5AC3}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5E4BDA70-F076-450B-A73E-034DF187DDD0}" name="FA1" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{728A5178-5E49-485C-811A-814C878280BD}" name="FA2" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{6512D9A4-ABA5-4A7F-B552-9FA02CBFBA15}" name="FA3" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{E3480F72-1A04-4419-A55B-8A371BCB83BB}" name="FA4" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{C5057181-6E4D-42CD-A672-89666A3A590F}" name="FA5" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{9E111813-83ED-4BC3-A5C2-2B23EDCBE045}" name="FA6" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{E3B443D2-6ABB-4DA9-85A3-23615366D11A}" name="FA7" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{9AD5DAC3-1F8A-44BE-8C81-D4E0724B6EED}" name="FA8" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{81F25ED4-3EA1-4016-930B-258B361297C7}" name="FA9" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{5E4BDA70-F076-450B-A73E-034DF187DDD0}" name="FA1" dataDxfId="112"/>
+    <tableColumn id="2" xr3:uid="{728A5178-5E49-485C-811A-814C878280BD}" name="FA2" dataDxfId="111"/>
+    <tableColumn id="3" xr3:uid="{6512D9A4-ABA5-4A7F-B552-9FA02CBFBA15}" name="FA3" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{E3480F72-1A04-4419-A55B-8A371BCB83BB}" name="FA4" dataDxfId="109"/>
+    <tableColumn id="5" xr3:uid="{C5057181-6E4D-42CD-A672-89666A3A590F}" name="FA5" dataDxfId="108"/>
+    <tableColumn id="6" xr3:uid="{9E111813-83ED-4BC3-A5C2-2B23EDCBE045}" name="FA6" dataDxfId="107"/>
+    <tableColumn id="7" xr3:uid="{E3B443D2-6ABB-4DA9-85A3-23615366D11A}" name="FA7" dataDxfId="106"/>
+    <tableColumn id="8" xr3:uid="{9AD5DAC3-1F8A-44BE-8C81-D4E0724B6EED}" name="FA8" dataDxfId="105"/>
+    <tableColumn id="9" xr3:uid="{81F25ED4-3EA1-4016-930B-258B361297C7}" name="FA9" dataDxfId="104"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2729,45 +3469,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H233"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="35" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2088701244</v>
       </c>
@@ -2781,7 +3521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2088701390</v>
       </c>
@@ -2795,7 +3535,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2088701610</v>
       </c>
@@ -2809,7 +3549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2088701746</v>
       </c>
@@ -2820,7 +3560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2088702198</v>
       </c>
@@ -2834,7 +3574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2088702199</v>
       </c>
@@ -2848,7 +3588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2088702200</v>
       </c>
@@ -2862,7 +3602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2088702201</v>
       </c>
@@ -2879,7 +3619,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2088702202</v>
       </c>
@@ -2893,7 +3633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2088702203</v>
       </c>
@@ -2907,7 +3647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2088702204</v>
       </c>
@@ -2921,7 +3661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2088702205</v>
       </c>
@@ -2935,7 +3675,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2088702206</v>
       </c>
@@ -2949,7 +3689,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2088702207</v>
       </c>
@@ -2975,7 +3715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2088702221</v>
       </c>
@@ -2989,7 +3729,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2088702318</v>
       </c>
@@ -3003,7 +3743,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2088707042</v>
       </c>
@@ -3017,7 +3757,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2098700024</v>
       </c>
@@ -3031,7 +3771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>2098700025</v>
       </c>
@@ -3045,7 +3785,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2098700026</v>
       </c>
@@ -3059,7 +3799,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2098700033</v>
       </c>
@@ -3073,7 +3813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2098700046</v>
       </c>
@@ -3087,7 +3827,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2098700056</v>
       </c>
@@ -3101,7 +3841,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2098700058</v>
       </c>
@@ -3115,7 +3855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2098700076</v>
       </c>
@@ -3129,7 +3869,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2098700083</v>
       </c>
@@ -3143,7 +3883,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>2098700108</v>
       </c>
@@ -3157,7 +3897,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2098700143</v>
       </c>
@@ -3171,7 +3911,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2098700154</v>
       </c>
@@ -3185,7 +3925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2098700177</v>
       </c>
@@ -3199,7 +3939,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2098700189</v>
       </c>
@@ -3213,7 +3953,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2098700245</v>
       </c>
@@ -3227,7 +3967,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>2098700246</v>
       </c>
@@ -3241,7 +3981,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>2098700256</v>
       </c>
@@ -3255,7 +3995,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2098700289</v>
       </c>
@@ -3269,7 +4009,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2098700290</v>
       </c>
@@ -3283,7 +4023,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2098700293</v>
       </c>
@@ -3297,7 +4037,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2098700296</v>
       </c>
@@ -3314,7 +4054,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2098700301</v>
       </c>
@@ -3328,7 +4068,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2098700302</v>
       </c>
@@ -3342,7 +4082,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2098700304</v>
       </c>
@@ -3356,7 +4096,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2098700305</v>
       </c>
@@ -3370,7 +4110,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2098700306</v>
       </c>
@@ -3384,7 +4124,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2098700307</v>
       </c>
@@ -3398,7 +4138,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2098700309</v>
       </c>
@@ -3412,7 +4152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2098700315</v>
       </c>
@@ -3426,7 +4166,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2098700316</v>
       </c>
@@ -3440,7 +4180,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2098700320</v>
       </c>
@@ -3454,7 +4194,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2098700322</v>
       </c>
@@ -3468,7 +4208,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2098700353</v>
       </c>
@@ -3482,7 +4222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2098700355</v>
       </c>
@@ -3496,7 +4236,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2098700356</v>
       </c>
@@ -3510,7 +4250,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2098700357</v>
       </c>
@@ -3524,7 +4264,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2098700358</v>
       </c>
@@ -3538,7 +4278,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2098700366</v>
       </c>
@@ -3552,7 +4292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2098700371</v>
       </c>
@@ -3566,7 +4306,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2098700372</v>
       </c>
@@ -3580,7 +4320,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2098700373</v>
       </c>
@@ -3594,7 +4334,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2098700374</v>
       </c>
@@ -3608,7 +4348,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2098700375</v>
       </c>
@@ -3622,7 +4362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2098700376</v>
       </c>
@@ -3636,7 +4376,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2098700378</v>
       </c>
@@ -3650,7 +4390,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>2098700379</v>
       </c>
@@ -3664,7 +4404,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>2098700380</v>
       </c>
@@ -3678,7 +4418,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>2098700404</v>
       </c>
@@ -3692,7 +4432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>2098700405</v>
       </c>
@@ -3706,7 +4446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2098700429</v>
       </c>
@@ -3720,7 +4460,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>2098700432</v>
       </c>
@@ -3734,7 +4474,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>2098700433</v>
       </c>
@@ -3748,7 +4488,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>2098700434</v>
       </c>
@@ -3762,7 +4502,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>2098700436</v>
       </c>
@@ -3776,7 +4516,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>2098700437</v>
       </c>
@@ -3793,7 +4533,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2098701682</v>
       </c>
@@ -3807,7 +4547,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>2098706005</v>
       </c>
@@ -3821,7 +4561,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>2098706008</v>
       </c>
@@ -3835,7 +4575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>2098706009</v>
       </c>
@@ -3849,7 +4589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2098706010</v>
       </c>
@@ -3863,7 +4603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2098706011</v>
       </c>
@@ -3877,7 +4617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2098706013</v>
       </c>
@@ -3891,7 +4631,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2098706018</v>
       </c>
@@ -3905,7 +4645,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2098706021</v>
       </c>
@@ -3919,7 +4659,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2098706023</v>
       </c>
@@ -3933,7 +4673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>2098706024</v>
       </c>
@@ -3947,7 +4687,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2098706025</v>
       </c>
@@ -3961,7 +4701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2098706026</v>
       </c>
@@ -3975,7 +4715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>2098706028</v>
       </c>
@@ -3989,7 +4729,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>2098706031</v>
       </c>
@@ -4003,7 +4743,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>2098706032</v>
       </c>
@@ -4017,7 +4757,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2098706040</v>
       </c>
@@ -4031,7 +4771,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>2098706041</v>
       </c>
@@ -4045,7 +4785,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>2098706044</v>
       </c>
@@ -4059,7 +4799,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>2098706072</v>
       </c>
@@ -4073,7 +4813,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>2098706075</v>
       </c>
@@ -4087,7 +4827,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>2098706076</v>
       </c>
@@ -4101,7 +4841,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>2098706083</v>
       </c>
@@ -4115,7 +4855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>2098706084</v>
       </c>
@@ -4129,7 +4869,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>2098706085</v>
       </c>
@@ -4143,7 +4883,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>2098706087</v>
       </c>
@@ -4157,7 +4897,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>2098706089</v>
       </c>
@@ -4171,7 +4911,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>2099700009</v>
       </c>
@@ -4185,7 +4925,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>2099700010</v>
       </c>
@@ -4199,7 +4939,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2099700025</v>
       </c>
@@ -4216,7 +4956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2099700030</v>
       </c>
@@ -4236,7 +4976,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>2099700041</v>
       </c>
@@ -4250,7 +4990,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>2099700048</v>
       </c>
@@ -4264,7 +5004,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>2099700049</v>
       </c>
@@ -4278,7 +5018,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>2099700056</v>
       </c>
@@ -4292,7 +5032,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>2099700057</v>
       </c>
@@ -4309,7 +5049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>2099700058</v>
       </c>
@@ -4332,7 +5072,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>2099700059</v>
       </c>
@@ -4355,7 +5095,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>2099706005</v>
       </c>
@@ -4369,7 +5109,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>2154140069</v>
       </c>
@@ -4383,7 +5123,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>2154140162</v>
       </c>
@@ -4397,7 +5137,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>2154140207</v>
       </c>
@@ -4411,7 +5151,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>2154140222</v>
       </c>
@@ -4425,7 +5165,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>2154140224</v>
       </c>
@@ -4439,7 +5179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>2154140225</v>
       </c>
@@ -4453,7 +5193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>2154140229</v>
       </c>
@@ -4467,7 +5207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>2154140243</v>
       </c>
@@ -4481,7 +5221,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2154140283</v>
       </c>
@@ -4495,7 +5235,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2154140284</v>
       </c>
@@ -4509,7 +5249,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>2154140285</v>
       </c>
@@ -4523,7 +5263,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2154140287</v>
       </c>
@@ -4537,7 +5277,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2154140289</v>
       </c>
@@ -4551,7 +5291,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>2154140290</v>
       </c>
@@ -4565,7 +5305,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>2154140291</v>
       </c>
@@ -4579,7 +5319,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>2154140292</v>
       </c>
@@ -4593,7 +5333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2154140293</v>
       </c>
@@ -4607,7 +5347,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2154140294</v>
       </c>
@@ -4621,7 +5361,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2154140295</v>
       </c>
@@ -4635,7 +5375,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>2154140318</v>
       </c>
@@ -4649,7 +5389,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>2154140319</v>
       </c>
@@ -4663,7 +5403,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>2154140335</v>
       </c>
@@ -4677,7 +5417,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>2154140336</v>
       </c>
@@ -4691,7 +5431,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>2154140345</v>
       </c>
@@ -4705,7 +5445,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>2154140349</v>
       </c>
@@ -4719,7 +5459,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>2154140596</v>
       </c>
@@ -4733,7 +5473,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>2154150035</v>
       </c>
@@ -4747,7 +5487,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>2154150089</v>
       </c>
@@ -4761,7 +5501,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2154150163</v>
       </c>
@@ -4775,7 +5515,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>2154150172</v>
       </c>
@@ -4789,7 +5529,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>2154150197</v>
       </c>
@@ -4803,7 +5543,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>2154150214</v>
       </c>
@@ -4817,7 +5557,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>2154150215</v>
       </c>
@@ -4831,7 +5571,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>2154150247</v>
       </c>
@@ -4845,7 +5585,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>2154150250</v>
       </c>
@@ -4859,7 +5599,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>2154150301</v>
       </c>
@@ -4873,7 +5613,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>2154150337</v>
       </c>
@@ -4887,7 +5627,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>2154150341</v>
       </c>
@@ -4901,7 +5641,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>2154150342</v>
       </c>
@@ -4915,7 +5655,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>2154150343</v>
       </c>
@@ -4929,7 +5669,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>2154150347</v>
       </c>
@@ -4943,7 +5683,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>2154150348</v>
       </c>
@@ -4957,7 +5697,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>2154150349</v>
       </c>
@@ -4971,7 +5711,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>2154150350</v>
       </c>
@@ -4988,7 +5728,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>2154150351</v>
       </c>
@@ -5002,7 +5742,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>2154150357</v>
       </c>
@@ -5019,7 +5759,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>2154150358</v>
       </c>
@@ -5033,7 +5773,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>2154150366</v>
       </c>
@@ -5050,7 +5790,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>2154150370</v>
       </c>
@@ -5064,7 +5804,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>2154150380</v>
       </c>
@@ -5078,7 +5818,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>2154150391</v>
       </c>
@@ -5092,7 +5832,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>2154150420</v>
       </c>
@@ -5106,7 +5846,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>2154150447</v>
       </c>
@@ -5120,7 +5860,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>2154150448</v>
       </c>
@@ -5134,7 +5874,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>2154150455</v>
       </c>
@@ -5151,7 +5891,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>2154150461</v>
       </c>
@@ -5165,7 +5905,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>2154150497</v>
       </c>
@@ -5179,7 +5919,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>2154150501</v>
       </c>
@@ -5193,7 +5933,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>2154150509</v>
       </c>
@@ -5207,7 +5947,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>2154150525</v>
       </c>
@@ -5224,7 +5964,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>2154150526</v>
       </c>
@@ -5238,7 +5978,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="5">
         <v>2154150534</v>
       </c>
@@ -5255,7 +5995,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>2154150554</v>
       </c>
@@ -5269,7 +6009,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="5">
         <v>2154150557</v>
       </c>
@@ -5283,7 +6023,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="5">
         <v>2154150560</v>
       </c>
@@ -5303,7 +6043,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>2154150563</v>
       </c>
@@ -5311,13 +6051,13 @@
         <v>379</v>
       </c>
       <c r="C178" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D178" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>2154150581</v>
       </c>
@@ -5331,7 +6071,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>2154150582</v>
       </c>
@@ -5345,7 +6085,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>2154150588</v>
       </c>
@@ -5359,7 +6099,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="5">
         <v>2154150591</v>
       </c>
@@ -5376,7 +6116,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>2154150597</v>
       </c>
@@ -5393,7 +6133,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>2154150603</v>
       </c>
@@ -5407,7 +6147,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>2154150605</v>
       </c>
@@ -5421,7 +6161,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="5">
         <v>2154150622</v>
       </c>
@@ -5435,7 +6175,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="5">
         <v>2154150627</v>
       </c>
@@ -5449,7 +6189,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>2154150633</v>
       </c>
@@ -5463,7 +6203,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>2154150646</v>
       </c>
@@ -5483,7 +6223,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>2154150648</v>
       </c>
@@ -5503,7 +6243,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>2154150653</v>
       </c>
@@ -5517,7 +6257,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>2154150669</v>
       </c>
@@ -5531,7 +6271,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>2154150672</v>
       </c>
@@ -5545,7 +6285,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="5">
         <v>2154150677</v>
       </c>
@@ -5556,13 +6296,13 @@
         <v>122</v>
       </c>
       <c r="D194" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E194" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>2154150706</v>
       </c>
@@ -5576,7 +6316,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>2154150707</v>
       </c>
@@ -5590,7 +6330,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>2154150715</v>
       </c>
@@ -5604,7 +6344,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="5">
         <v>2154150719</v>
       </c>
@@ -5618,7 +6358,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="5">
         <v>2154150731</v>
       </c>
@@ -5632,7 +6372,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="5">
         <v>2154150765</v>
       </c>
@@ -5652,7 +6392,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="5">
         <v>2154150767</v>
       </c>
@@ -5672,7 +6412,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="5">
         <v>2154150769</v>
       </c>
@@ -5689,7 +6429,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="5">
         <v>2154150788</v>
       </c>
@@ -5703,7 +6443,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="5">
         <v>2154150813</v>
       </c>
@@ -5723,7 +6463,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="5">
         <v>2154150814</v>
       </c>
@@ -5740,7 +6480,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>2154150822</v>
       </c>
@@ -5757,7 +6497,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>2154150839</v>
       </c>
@@ -5771,7 +6511,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>2154150840</v>
       </c>
@@ -5785,7 +6525,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>2154150841</v>
       </c>
@@ -5799,7 +6539,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="5">
         <v>2154150876</v>
       </c>
@@ -5813,7 +6553,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="5">
         <v>2154150893</v>
       </c>
@@ -5827,7 +6567,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="5">
         <v>2154150918</v>
       </c>
@@ -5841,7 +6581,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="5">
         <v>2154150921</v>
       </c>
@@ -5855,7 +6595,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="5">
         <v>2154150922</v>
       </c>
@@ -5869,7 +6609,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>2154150943</v>
       </c>
@@ -5883,7 +6623,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>2154155136</v>
       </c>
@@ -5897,7 +6637,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="5">
         <v>2154155149</v>
       </c>
@@ -5911,7 +6651,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="5">
         <v>2154155150</v>
       </c>
@@ -5928,7 +6668,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>2154160029</v>
       </c>
@@ -5942,7 +6682,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>2154160030</v>
       </c>
@@ -5956,7 +6696,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>2154160031</v>
       </c>
@@ -5970,7 +6710,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>2154160032</v>
       </c>
@@ -5984,7 +6724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>2154160033</v>
       </c>
@@ -5998,7 +6738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>2154160034</v>
       </c>
@@ -6012,7 +6752,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>2154160035</v>
       </c>
@@ -6026,7 +6766,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>2154160036</v>
       </c>
@@ -6040,7 +6780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>2154160037</v>
       </c>
@@ -6054,7 +6794,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>2154170049</v>
       </c>
@@ -6068,7 +6808,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>2154170050</v>
       </c>
@@ -6091,7 +6831,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>2154170052</v>
       </c>
@@ -6105,7 +6845,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
     </row>
@@ -6124,1267 +6864,1270 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:CW10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <dimension ref="A1:CX10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="61" max="62" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="12" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="75" max="76" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="12" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="89" max="90" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="12" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.6328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.6328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.6328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.6328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.6328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12" style="39" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.08984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.6328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="12.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.6328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="11.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="12.90625" style="39" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="12" style="39" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.08984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="75" max="76" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="11.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="12" style="39" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="12.08984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="89" max="90" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="12" style="39" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="12.08984375" style="39" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="12.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="13.36328125" style="39" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="13" style="39" bestFit="1" customWidth="1"/>
+    <col min="103" max="16384" width="8.7265625" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:101" ht="15">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AG1" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AH1" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AI1" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AJ1" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AL1" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AM1" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AN1" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AO1" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AP1" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AQ1" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AR1" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AS1" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AT1" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AU1" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AV1" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AW1" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AX1" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AY1" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="AZ1" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BA1" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BB1" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BC1" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BD1" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BE1" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BF1" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BG1" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BH1" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BI1" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BJ1" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BK1" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BL1" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BM1" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BN1" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BO1" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BP1" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BQ1" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BR1" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BS1" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BT1" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BU1" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BV1" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BW1" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BX1" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="BY1" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="BZ1" s="6" t="s">
+      <c r="BZ1" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CA1" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="CB1" s="6" t="s">
+      <c r="CB1" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="CC1" s="6" t="s">
+      <c r="CC1" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="CD1" s="6" t="s">
+      <c r="CD1" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="CE1" s="6" t="s">
+      <c r="CE1" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="CF1" s="6" t="s">
+      <c r="CF1" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="CG1" s="6" t="s">
+      <c r="CG1" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="CH1" s="6" t="s">
+      <c r="CH1" s="38" t="s">
         <v>247</v>
       </c>
-      <c r="CI1" s="6" t="s">
+      <c r="CI1" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="CJ1" s="6" t="s">
+      <c r="CJ1" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="CK1" s="6" t="s">
+      <c r="CK1" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="CL1" s="6" t="s">
+      <c r="CL1" s="38" t="s">
         <v>251</v>
       </c>
-      <c r="CM1" s="6" t="s">
+      <c r="CM1" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="CN1" s="6" t="s">
+      <c r="CN1" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="CO1" s="6" t="s">
+      <c r="CO1" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="CP1" s="6" t="s">
+      <c r="CP1" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="CQ1" s="6" t="s">
+      <c r="CQ1" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="CR1" s="6" t="s">
+      <c r="CR1" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="CS1" s="6" t="s">
+      <c r="CS1" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="CT1" s="6" t="s">
+      <c r="CT1" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="CU1" s="6" t="s">
+      <c r="CU1" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="CV1" s="6" t="s">
+      <c r="CV1" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="CW1" s="6" t="s">
+      <c r="CW1" s="38" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="2" spans="1:101">
-      <c r="A2" t="s">
+      <c r="CX1" s="38" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="2" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A2" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="36" t="s">
+      <c r="H2" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="39" t="s">
         <v>266</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="P2" s="36" t="s">
+      <c r="P2" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="Q2" s="36" t="s">
+      <c r="Q2" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="R2" s="36" t="s">
+      <c r="R2" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="S2" s="36" t="s">
+      <c r="S2" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="T2" s="36" t="s">
+      <c r="T2" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="U2" s="36" t="s">
+      <c r="U2" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="V2" s="36" t="s">
+      <c r="V2" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="W2" s="36" t="s">
+      <c r="W2" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="X2" s="36" t="s">
+      <c r="X2" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="Y2" s="36" t="s">
+      <c r="Y2" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="Z2" s="36" t="s">
+      <c r="Z2" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="AA2" s="36" t="s">
+      <c r="AA2" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="AB2" s="36" t="s">
+      <c r="AB2" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="AC2" s="36" t="s">
+      <c r="AC2" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="AD2" s="36" t="s">
+      <c r="AD2" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="AE2" s="36" t="s">
+      <c r="AE2" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="AF2" s="36" t="s">
+      <c r="AF2" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="AG2" s="36" t="s">
+      <c r="AG2" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="AH2" s="36" t="s">
+      <c r="AH2" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="AI2" s="36" t="s">
+      <c r="AI2" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="AJ2" s="36" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="AK2" s="36" t="s">
+      <c r="AK2" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="AL2" s="36" t="s">
+      <c r="AL2" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="AM2" s="36" t="s">
+      <c r="AM2" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="AN2" s="36" t="s">
+      <c r="AN2" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="AO2" s="36" t="s">
+      <c r="AO2" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="AP2" s="36" t="s">
+      <c r="AP2" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="AQ2" s="36" t="s">
+      <c r="AQ2" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="AR2" s="36" t="s">
+      <c r="AR2" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="AS2" s="36" t="s">
+      <c r="AS2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="AT2" s="36" t="s">
+      <c r="AT2" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="AU2" s="36" t="s">
+      <c r="AU2" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="AV2" s="36" t="s">
+      <c r="AV2" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="AW2" s="36" t="s">
+      <c r="AW2" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="AX2" s="36" t="s">
+      <c r="AX2" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="AY2" s="36" t="s">
+      <c r="AY2" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="AZ2" s="36" t="s">
+      <c r="AZ2" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="BA2" s="36" t="s">
+      <c r="BA2" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="BB2" s="36" t="s">
+      <c r="BB2" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="BC2" s="36" t="s">
+      <c r="BC2" s="39" t="s">
         <v>284</v>
       </c>
-      <c r="BD2" s="36" t="s">
+      <c r="BD2" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="BE2" s="36" t="s">
+      <c r="BE2" s="39" t="s">
         <v>286</v>
       </c>
-      <c r="BF2" s="36" t="s">
+      <c r="BF2" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="BG2" s="36" t="s">
+      <c r="BG2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="BH2" s="36" t="s">
+      <c r="BH2" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="BI2" s="36" t="s">
+      <c r="BI2" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="BJ2" s="36" t="s">
+      <c r="BJ2" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="BK2" s="36" t="s">
+      <c r="BK2" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="BL2" s="36" t="s">
+      <c r="BL2" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="BM2" s="36" t="s">
+      <c r="BM2" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="BN2" s="36" t="s">
+      <c r="BN2" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="BO2" s="36" t="s">
+      <c r="BO2" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="BP2" s="36" t="s">
+      <c r="BP2" s="39" t="s">
         <v>292</v>
       </c>
-      <c r="BQ2" s="36" t="s">
+      <c r="BQ2" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="BR2" s="36" t="s">
+      <c r="BR2" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="BS2" s="36" t="s">
+      <c r="BS2" s="39" t="s">
         <v>295</v>
       </c>
-      <c r="BT2" s="36" t="s">
+      <c r="BT2" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="BU2" s="36" t="s">
+      <c r="BU2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="BV2" s="36" t="s">
+      <c r="BV2" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="BW2" s="36" t="s">
+      <c r="BW2" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="BX2" s="36" t="s">
+      <c r="BX2" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="BY2" s="36" t="s">
+      <c r="BY2" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="BZ2" s="36" t="s">
+      <c r="BZ2" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="CA2" s="36" t="s">
+      <c r="CA2" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="CB2" s="36" t="s">
+      <c r="CB2" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="CC2" s="36" t="s">
+      <c r="CC2" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="CD2" s="36" t="s">
+      <c r="CD2" s="39" t="s">
         <v>292</v>
       </c>
-      <c r="CE2" s="36" t="s">
+      <c r="CE2" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="CF2" s="36" t="s">
+      <c r="CF2" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="CG2" s="36" t="s">
+      <c r="CG2" s="39" t="s">
         <v>295</v>
       </c>
-      <c r="CH2" s="36" t="s">
+      <c r="CH2" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="CI2" s="36" t="s">
+      <c r="CI2" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="CJ2" s="36" t="s">
+      <c r="CJ2" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="CK2" s="36" t="s">
+      <c r="CK2" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="CL2" s="36" t="s">
+      <c r="CL2" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="CM2" s="36" t="s">
+      <c r="CM2" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="CN2" s="36" t="s">
+      <c r="CN2" s="39" t="s">
         <v>301</v>
       </c>
-      <c r="CO2" s="36" t="s">
+      <c r="CO2" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="CP2" s="36" t="s">
+      <c r="CP2" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="CQ2" s="36" t="s">
+      <c r="CQ2" s="39" t="s">
         <v>304</v>
       </c>
-      <c r="CR2" s="36" t="s">
+      <c r="CR2" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="CS2" s="36" t="s">
+      <c r="CS2" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="CT2" s="36" t="s">
+      <c r="CT2" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="CU2" s="36" t="s">
+      <c r="CU2" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="CV2" s="36" t="s">
+      <c r="CV2" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="CW2" s="36" t="s">
+      <c r="CW2" s="39" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="3" spans="1:101">
-      <c r="A3" t="s">
+      <c r="CX2" s="40" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A3" s="39" t="s">
         <v>310</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>402</v>
-      </c>
-      <c r="D3" s="36" t="s">
+      <c r="C3" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="41" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:101">
-      <c r="A4" t="s">
+    <row r="4" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="39" t="s">
         <v>313</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="41" t="s">
         <v>412</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="O4" s="37" t="s">
+      <c r="O4" s="42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:101">
-      <c r="A5" t="s">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A5" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="39" t="s">
         <v>315</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="K5" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="36" t="s">
+      <c r="L5" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="36" t="s">
+      <c r="M5" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="N5" s="36" t="s">
+      <c r="N5" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="O5" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="36" t="s">
+      <c r="P5" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="Q5" s="36" t="s">
+      <c r="Q5" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="R5" s="36" t="s">
+      <c r="R5" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="S5" s="36" t="s">
+      <c r="S5" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="T5" s="36" t="s">
+      <c r="T5" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="U5" s="36" t="s">
+      <c r="U5" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="V5" s="36" t="s">
+      <c r="V5" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="W5" s="36" t="s">
+      <c r="W5" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="X5" s="36" t="s">
+      <c r="X5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="36" t="s">
+      <c r="Y5" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="Z5" s="36" t="s">
+      <c r="Z5" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="AA5" s="36" t="s">
+      <c r="AA5" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="AB5" s="36" t="s">
+      <c r="AB5" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="AC5" s="36" t="s">
+      <c r="AC5" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="AD5" s="36" t="s">
+      <c r="AD5" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="AE5" s="37" t="s">
+      <c r="AE5" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AF5" s="41" t="s">
         <v>358</v>
       </c>
-      <c r="AG5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="6" spans="1:101">
-      <c r="A6" t="s">
+      <c r="AG5" s="41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A6" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="39" t="s">
         <v>317</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="H6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="36" t="s">
+      <c r="J6" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="K6" s="36" t="s">
+      <c r="K6" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="L6" s="36" t="s">
+      <c r="L6" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="M6" s="36" t="s">
+      <c r="M6" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="N6" s="36" t="s">
+      <c r="N6" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="O6" s="36" t="s">
+      <c r="O6" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="P6" s="36" t="s">
+      <c r="P6" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="Q6" s="36" t="s">
+      <c r="Q6" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="R6" s="36" t="s">
+      <c r="R6" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="S6" s="36" t="s">
+      <c r="S6" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="T6" s="36" t="s">
+      <c r="T6" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="U6" s="36" t="s">
+      <c r="U6" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="V6" s="36" t="s">
+      <c r="V6" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="36" t="s">
+      <c r="W6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="X6" s="36" t="s">
-        <v>429</v>
-      </c>
-      <c r="Y6" s="36" t="s">
+      <c r="X6" s="41" t="s">
+        <v>428</v>
+      </c>
+      <c r="Y6" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="Z6" s="37" t="s">
+      <c r="Z6" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="AA6" s="37" t="s">
+      <c r="AA6" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="AB6" s="36" t="s">
+      <c r="AB6" s="41" t="s">
         <v>358</v>
       </c>
-      <c r="AC6" s="36" t="s">
+      <c r="AC6" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="AD6" s="37" t="s">
+      <c r="AD6" s="42" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:101">
-      <c r="A7" t="s">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A7" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="F7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="G7" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="L7" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="M7" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="O7" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="P7" s="42" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q7" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="R7" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>374</v>
-      </c>
-      <c r="H7" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="I7" s="40" t="s">
+      <c r="S7" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="U7" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="V7" s="42" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A8" s="39" t="s">
+        <v>320</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="J8" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="K8" s="41" t="s">
+        <v>368</v>
+      </c>
+      <c r="L8" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q8" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" s="42" t="s">
+        <v>359</v>
+      </c>
+      <c r="S8" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+    </row>
+    <row r="9" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A9" s="39" t="s">
+        <v>322</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>323</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="K9" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="L9" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="N9" s="41" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A10" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>325</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="K7" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="L7" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="M7" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="P7" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q7" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="R7" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="S7" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="T7" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="U7" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="V7" s="41" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="8" spans="1:101">
-      <c r="A8" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" t="s">
-        <v>321</v>
-      </c>
-      <c r="C8" s="36" t="s">
+      <c r="E10" s="41" t="s">
+        <v>365</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>369</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="36" t="s">
+      <c r="H10" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="K10" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="L10" s="41" t="s">
+        <v>372</v>
+      </c>
+      <c r="M10" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="N10" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="O10" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="P10" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q10" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="R10" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="S10" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="41" t="s">
+        <v>414</v>
+      </c>
+      <c r="U10" s="41" t="s">
+        <v>414</v>
+      </c>
+      <c r="V10" s="41" t="s">
+        <v>372</v>
+      </c>
+      <c r="W10" s="41" t="s">
+        <v>411</v>
+      </c>
+      <c r="X10" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y10" s="41" t="s">
+        <v>413</v>
+      </c>
+      <c r="Z10" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>373</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>368</v>
-      </c>
-      <c r="L8" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="N8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="P8" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q8" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="R8" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="S8" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-    </row>
-    <row r="9" spans="1:101">
-      <c r="A9" t="s">
-        <v>322</v>
-      </c>
-      <c r="B9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="J9" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="K9" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="L9" s="43" t="s">
+      <c r="AA10" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="M9" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="N9" s="43" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:101">
-      <c r="A10" t="s">
-        <v>426</v>
-      </c>
-      <c r="B10" t="s">
-        <v>325</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>365</v>
-      </c>
-      <c r="D10" s="36" t="s">
+      <c r="AB10" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="AC10" s="41" t="s">
+        <v>358</v>
+      </c>
+      <c r="AD10" s="41" t="s">
+        <v>362</v>
+      </c>
+      <c r="AE10" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>365</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>329</v>
-      </c>
-      <c r="L10" s="34" t="s">
-        <v>372</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>373</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="O10" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="P10" s="34" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q10" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>360</v>
-      </c>
-      <c r="S10" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="T10" s="34" t="s">
-        <v>414</v>
-      </c>
-      <c r="U10" s="34" t="s">
-        <v>414</v>
-      </c>
-      <c r="V10" s="34" t="s">
-        <v>372</v>
-      </c>
-      <c r="W10" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="X10" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y10" s="34" t="s">
-        <v>413</v>
-      </c>
-      <c r="Z10" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA10" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB10" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="AC10" s="34" t="s">
-        <v>358</v>
-      </c>
-      <c r="AD10" s="34" t="s">
-        <v>362</v>
-      </c>
-      <c r="AE10" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF10" s="34" t="s">
+      <c r="AF10" s="41" t="s">
         <v>419</v>
       </c>
-      <c r="AG10" s="34" t="s">
+      <c r="AG10" s="41" t="s">
         <v>361</v>
       </c>
-      <c r="AH10" s="34" t="s">
+      <c r="AH10" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="AI10" s="34"/>
-      <c r="AJ10" s="34"/>
-      <c r="AK10" s="34"/>
-      <c r="AL10" s="34"/>
-      <c r="AM10" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -7398,13 +8141,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AZ11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="52" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="52" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="15">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7514,680 +8257,680 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:52" ht="15">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="36">
+        <v>425</v>
+      </c>
+      <c r="B2" s="34">
         <v>2099700058</v>
       </c>
-      <c r="C2" s="36">
+      <c r="C2" s="34">
         <v>2099700059</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="34">
         <v>2098700436</v>
       </c>
-      <c r="E2" s="36">
+      <c r="E2" s="34">
         <v>2098706085</v>
       </c>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="39"/>
-    </row>
-    <row r="3" spans="1:52">
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>262</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="34" t="s">
         <v>333</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="36" t="s">
+      <c r="K3" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="34" t="s">
         <v>335</v>
       </c>
-      <c r="M3" s="36" t="s">
+      <c r="M3" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="N3" s="36">
+      <c r="N3" s="34">
         <v>2098700076</v>
       </c>
-      <c r="O3" s="36" t="s">
+      <c r="O3" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="36" t="s">
+      <c r="P3" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="36" t="s">
+      <c r="Q3" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="R3" s="36" t="s">
+      <c r="R3" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="S3" s="36" t="s">
+      <c r="S3" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="T3" s="36" t="s">
+      <c r="T3" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="U3" s="36" t="s">
+      <c r="U3" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="V3" s="36" t="s">
+      <c r="V3" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="W3" s="36" t="s">
+      <c r="W3" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="X3" s="36" t="s">
+      <c r="X3" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="Y3" s="36" t="s">
+      <c r="Y3" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="Z3" s="36" t="s">
+      <c r="Z3" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="AA3" s="36" t="s">
+      <c r="AA3" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="AB3" s="36" t="s">
+      <c r="AB3" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AC3" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="AD3" s="36" t="s">
+      <c r="AD3" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="AE3" s="36">
+      <c r="AE3" s="34">
         <v>2088702318</v>
       </c>
-      <c r="AF3" s="36">
+      <c r="AF3" s="34">
         <v>2088706010</v>
       </c>
-      <c r="AG3" s="36">
+      <c r="AG3" s="34">
         <v>2098700429</v>
       </c>
-      <c r="AH3" s="36">
+      <c r="AH3" s="34">
         <v>2088701610</v>
       </c>
-      <c r="AI3" s="36">
+      <c r="AI3" s="34">
         <v>2098700189</v>
       </c>
     </row>
-    <row r="4" spans="1:52">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>310</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="N4" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="O4" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="34">
         <v>2154140336</v>
       </c>
       <c r="Q4">
         <v>2088701610</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="34">
         <v>2154150715</v>
       </c>
     </row>
-    <row r="5" spans="1:52">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>312</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="34">
         <v>2003020640</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="K5" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="L5" s="36" t="s">
+      <c r="L5" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="M5" s="36" t="s">
+      <c r="M5" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="N5" s="36" t="s">
+      <c r="N5" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="O5" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="P5" s="36" t="s">
+      <c r="P5" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="Q5" s="36">
+      <c r="Q5" s="34">
         <v>2098700305</v>
       </c>
-      <c r="R5" s="36">
+      <c r="R5" s="34">
         <v>2098706018</v>
       </c>
-      <c r="S5" s="36">
+      <c r="S5" s="34">
         <v>2098706011</v>
       </c>
-      <c r="T5" s="36">
+      <c r="T5" s="34">
         <v>2088702199</v>
       </c>
-      <c r="U5" s="36">
+      <c r="U5" s="34">
         <v>2098706010</v>
       </c>
     </row>
-    <row r="6" spans="1:52">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>314</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="34" t="s">
         <v>337</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="H6" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="J6" s="36" t="s">
+      <c r="J6" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="K6" s="36" t="s">
+      <c r="K6" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="L6" s="36" t="s">
+      <c r="L6" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="M6" s="36" t="s">
+      <c r="M6" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="N6" s="36" t="s">
+      <c r="N6" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="O6" s="36" t="s">
+      <c r="O6" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="P6" s="36" t="s">
+      <c r="P6" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="Q6" s="36" t="s">
+      <c r="Q6" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="R6" s="36">
+      <c r="R6" s="34">
         <v>2154160034</v>
       </c>
-      <c r="S6" s="36" t="s">
+      <c r="S6" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="T6" s="36">
+      <c r="T6" s="34">
         <v>2098700256</v>
       </c>
-      <c r="U6" s="36">
+      <c r="U6" s="34">
         <v>2098700304</v>
       </c>
-      <c r="V6" s="36" t="s">
+      <c r="V6" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="W6" s="36" t="s">
+      <c r="W6" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="X6" s="36">
+      <c r="X6" s="34">
         <v>2098700432</v>
       </c>
-      <c r="Y6" s="36">
+      <c r="Y6" s="34">
         <v>2098700433</v>
       </c>
-      <c r="Z6" s="36">
+      <c r="Z6" s="34">
         <v>2098700434</v>
       </c>
-      <c r="AA6" s="36">
+      <c r="AA6" s="34">
         <v>2154140324</v>
       </c>
-      <c r="AB6" s="36">
+      <c r="AB6" s="34">
         <v>2154150497</v>
       </c>
-      <c r="AC6" s="36">
+      <c r="AC6" s="34">
         <v>2088702198</v>
       </c>
     </row>
-    <row r="7" spans="1:52">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>316</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="36" t="s">
+      <c r="K7" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="L7" s="36" t="s">
+      <c r="L7" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="M7" s="36" t="s">
+      <c r="M7" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="N7" s="36" t="s">
+      <c r="N7" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="O7" s="36" t="s">
+      <c r="O7" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="P7" s="36" t="s">
+      <c r="P7" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="Q7" s="36" t="s">
+      <c r="Q7" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="R7" s="36" t="s">
+      <c r="R7" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="S7" s="36" t="s">
+      <c r="S7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="36" t="s">
+      <c r="T7" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="U7" s="36" t="s">
+      <c r="U7" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="V7" s="36" t="s">
+      <c r="V7" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="W7" s="36" t="s">
+      <c r="W7" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="X7" s="36" t="s">
+      <c r="X7" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="Y7" s="36" t="s">
+      <c r="Y7" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="Z7" s="36" t="s">
+      <c r="Z7" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="AA7" s="36" t="s">
+      <c r="AA7" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="AB7" s="36" t="s">
+      <c r="AB7" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="AC7" s="36" t="s">
+      <c r="AC7" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="AD7" s="36" t="s">
+      <c r="AD7" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="AE7" s="36" t="s">
+      <c r="AE7" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="AF7" s="36" t="s">
+      <c r="AF7" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="AG7" s="36" t="s">
+      <c r="AG7" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="AH7" s="36" t="s">
+      <c r="AH7" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="AI7" s="36" t="s">
+      <c r="AI7" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="AJ7" s="36" t="s">
+      <c r="AJ7" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="AK7" s="36">
+      <c r="AK7" s="34">
         <v>2098700379</v>
       </c>
-      <c r="AL7" s="36">
+      <c r="AL7" s="34">
         <v>2098700380</v>
       </c>
-      <c r="AM7" s="36">
+      <c r="AM7" s="34">
         <v>2098706024</v>
       </c>
-      <c r="AN7" s="36">
+      <c r="AN7" s="34">
         <v>2098706072</v>
       </c>
-      <c r="AO7" s="36">
+      <c r="AO7" s="34">
         <v>2098706075</v>
       </c>
-      <c r="AP7" s="36">
+      <c r="AP7" s="34">
         <v>2098706086</v>
       </c>
-      <c r="AQ7" s="36">
+      <c r="AQ7" s="34">
         <v>2098706087</v>
       </c>
-      <c r="AR7" s="36">
+      <c r="AR7" s="34">
         <v>2098706088</v>
       </c>
-      <c r="AS7" s="36">
+      <c r="AS7" s="34">
         <v>2098706089</v>
       </c>
-      <c r="AT7" s="36">
+      <c r="AT7" s="34">
         <v>2154140596</v>
       </c>
-      <c r="AU7" s="36">
+      <c r="AU7" s="34">
         <v>2098700434</v>
       </c>
-      <c r="AV7" s="36">
+      <c r="AV7" s="34">
         <v>2098700436</v>
       </c>
-      <c r="AW7" s="36">
+      <c r="AW7" s="34">
         <v>2098700256</v>
       </c>
-      <c r="AX7" s="36">
+      <c r="AX7" s="34">
         <v>2098700432</v>
       </c>
-      <c r="AY7" s="36">
+      <c r="AY7" s="34">
         <v>2098700433</v>
       </c>
-      <c r="AZ7" s="36">
+      <c r="AZ7" s="34">
         <v>2088701390</v>
       </c>
     </row>
-    <row r="8" spans="1:52">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>318</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="34" t="s">
         <v>341</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="I8" s="36" t="s">
+      <c r="I8" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="K8" s="36" t="s">
+      <c r="K8" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="L8" s="36" t="s">
+      <c r="L8" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="M8" s="36" t="s">
+      <c r="M8" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="N8" s="36" t="s">
+      <c r="N8" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="O8" s="36" t="s">
+      <c r="O8" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="P8" s="36" t="s">
+      <c r="P8" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="Q8" s="36" t="s">
+      <c r="Q8" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="R8" s="36">
+      <c r="R8" s="34">
         <v>2154150840</v>
       </c>
-      <c r="S8" s="36">
+      <c r="S8" s="34">
         <v>2154150876</v>
       </c>
-      <c r="T8" s="36">
+      <c r="T8" s="34">
         <v>2154160037</v>
       </c>
-      <c r="U8" s="36">
+      <c r="U8" s="34">
         <v>2088702199</v>
       </c>
-      <c r="V8" s="36">
+      <c r="V8" s="34">
         <v>2088702200</v>
       </c>
-      <c r="W8" s="36">
+      <c r="W8" s="34">
         <v>2088702207</v>
       </c>
-      <c r="X8" s="36">
+      <c r="X8" s="34">
         <v>2088702221</v>
       </c>
-      <c r="Y8" s="36">
+      <c r="Y8" s="34">
         <v>2088702318</v>
       </c>
-      <c r="Z8" s="36">
+      <c r="Z8" s="34">
         <v>2088707042</v>
       </c>
     </row>
-    <row r="9" spans="1:52">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>320</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="I9" s="36" t="s">
+      <c r="I9" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="K9" s="36" t="s">
+      <c r="K9" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="34">
         <v>2154150788</v>
       </c>
-      <c r="M9" s="36">
+      <c r="M9" s="34">
         <v>2154160037</v>
       </c>
-      <c r="N9" s="36">
+      <c r="N9" s="34">
         <v>2098700437</v>
       </c>
     </row>
-    <row r="10" spans="1:52">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>322</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="34">
         <v>2099700057</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="34">
         <v>2154170049</v>
       </c>
     </row>
-    <row r="11" spans="1:52">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>324</v>
       </c>
@@ -8200,12 +8943,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="66.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>342</v>
       </c>
@@ -8213,7 +8956,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>323</v>
       </c>
@@ -8221,7 +8964,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>315</v>
       </c>
@@ -8229,7 +8972,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>319</v>
       </c>
@@ -8237,7 +8980,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>347</v>
       </c>
@@ -8245,7 +8988,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>315</v>
       </c>
@@ -8253,7 +8996,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>350</v>
       </c>
@@ -8261,7 +9004,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>323</v>
       </c>
@@ -8269,7 +9012,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>317</v>
       </c>
@@ -8277,7 +9020,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>315</v>
       </c>
@@ -8285,7 +9028,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>315</v>
       </c>
@@ -8293,7 +9036,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -8301,7 +9044,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>421</v>
       </c>
@@ -8309,20 +9052,20 @@
         <v>422</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>325</v>
       </c>
       <c r="B14" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>317</v>
       </c>
       <c r="B15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -8333,935 +9076,935 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA531276-FCFB-48E9-A31C-F81A22563EEA}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="40.5">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="J3" s="37" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="40.5">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A4" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="J4" s="42" t="s">
+      <c r="J4" s="37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="40.5">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A5" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="37" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="60.75">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:10" ht="80" x14ac:dyDescent="0.35">
+      <c r="A6" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="J6" s="42" t="s">
+      <c r="J6" s="37" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="40.5">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A7" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="42" t="s">
+      <c r="J7" s="37" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="40.5">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="J8" s="42" t="s">
+      <c r="J8" s="37" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="40.5">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="J9" s="42" t="s">
+      <c r="J9" s="37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="40.5">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="J10" s="42" t="s">
+      <c r="J10" s="37" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="40.5">
-      <c r="A11" s="21"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="17" t="s">
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A11" s="20"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="J11" s="42" t="s">
+      <c r="J11" s="37" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="60.75">
-      <c r="A12" s="21"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="17" t="s">
+    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A12" s="20"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="J12" s="42" t="s">
+      <c r="J12" s="37" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="40.5">
-      <c r="A13" s="21"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="17" t="s">
+    <row r="13" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A13" s="20"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="J13" s="42" t="s">
+      <c r="J13" s="37" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="40.5">
-      <c r="A14" s="21"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="17" t="s">
+    <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A14" s="20"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="J14" s="42" t="s">
+      <c r="J14" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="40.5">
-      <c r="A15" s="21"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="17" t="s">
+    <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A15" s="20"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="18" t="s">
+      <c r="H15" s="19"/>
+      <c r="I15" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="J15" s="42" t="s">
+      <c r="J15" s="37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="40.5">
-      <c r="A16" s="21"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="17" t="s">
+    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A16" s="20"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="18" t="s">
+      <c r="H16" s="19"/>
+      <c r="I16" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="J16" s="42" t="s">
+      <c r="J16" s="37" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="40.5">
-      <c r="A17" s="21"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="17" t="s">
+    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A17" s="20"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="18" t="s">
+      <c r="H17" s="19"/>
+      <c r="I17" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="J17" s="42" t="s">
+      <c r="J17" s="37" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="40.5">
-      <c r="A18" s="21"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="17" t="s">
+    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A18" s="20"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="18" t="s">
+      <c r="H18" s="19"/>
+      <c r="I18" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="J18" s="42" t="s">
+      <c r="J18" s="37" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="40.5">
-      <c r="A19" s="21"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="17" t="s">
+    <row r="19" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A19" s="20"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="17" t="s">
+      <c r="G19" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="18" t="s">
+      <c r="H19" s="19"/>
+      <c r="I19" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="J19" s="42" t="s">
+      <c r="J19" s="37" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="60.75">
-      <c r="A20" s="21"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="17" t="s">
+    <row r="20" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A20" s="20"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="H20" s="20"/>
-      <c r="I20" s="18" t="s">
+      <c r="H20" s="19"/>
+      <c r="I20" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="J20" s="42" t="s">
+      <c r="J20" s="37" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="60.75">
-      <c r="A21" s="21"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="17" t="s">
+    <row r="21" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A21" s="20"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="23" t="s">
+      <c r="H21" s="19"/>
+      <c r="I21" s="22" t="s">
         <v>414</v>
       </c>
-      <c r="J21" s="42" t="s">
+      <c r="J21" s="37" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="60.75">
-      <c r="A22" s="21"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="17" t="s">
+    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A22" s="20"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="23" t="s">
+      <c r="G22" s="18"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="22" t="s">
         <v>414</v>
       </c>
-      <c r="J22" s="42" t="s">
+      <c r="J22" s="37" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="60.75">
-      <c r="A23" s="21"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="17" t="s">
+    <row r="23" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A23" s="20"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="18" t="s">
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="J23" s="42" t="s">
+      <c r="J23" s="37" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="60.75">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="27" t="s">
+    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="28" t="s">
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="J24" s="42" t="s">
+      <c r="J24" s="37" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="60.75">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="24" t="s">
+    <row r="25" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="26" t="s">
         <v>357</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="30" t="s">
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="29" t="s">
         <v>416</v>
       </c>
-      <c r="J25" s="42" t="s">
+      <c r="J25" s="37" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="40.5">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="24" t="s">
+    <row r="26" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="18" t="s">
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="J26" s="42" t="s">
+      <c r="J26" s="37" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="40.5">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="24" t="s">
+    <row r="27" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="30" t="s">
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="J27" s="42" t="s">
+      <c r="J27" s="37" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="40.5">
-      <c r="A28" s="21"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="24" t="s">
+    <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A28" s="20"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="30" t="s">
+      <c r="E28" s="18"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="J28" s="42" t="s">
+      <c r="J28" s="37" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="40.5">
-      <c r="A29" s="21"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="17" t="s">
+    <row r="29" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A29" s="20"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="30" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="J29" s="42" t="s">
+      <c r="J29" s="37" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="40.5">
-      <c r="A30" s="21"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="17" t="s">
+    <row r="30" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A30" s="20"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="18" t="s">
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="J30" s="42" t="s">
+      <c r="J30" s="37" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="40.5">
-      <c r="A31" s="21"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="22" t="s">
+    <row r="31" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A31" s="20"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="18" t="s">
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="J31" s="42" t="s">
+      <c r="J31" s="37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="40.5">
-      <c r="A32" s="21"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="17" t="s">
+    <row r="32" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A32" s="20"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="18" t="s">
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="J32" s="42" t="s">
+      <c r="J32" s="37" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="40.5">
-      <c r="A33" s="21"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="17" t="s">
+    <row r="33" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A33" s="20"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="18" t="s">
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="J33" s="42" t="s">
+      <c r="J33" s="37" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="40.5">
-      <c r="A34" s="21"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="30" t="s">
+    <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.35">
+      <c r="A34" s="20"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="29" t="s">
         <v>418</v>
       </c>
-      <c r="J34" s="42" t="s">
+      <c r="J34" s="37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="21"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="18" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="20"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="21"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="18" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="20"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="21"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="18" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="20"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="17" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="21"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="18" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="20"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="17" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="21"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="18" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="20"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="17" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" thickBot="1">
-      <c r="A40" s="31"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="33" t="s">
+    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="30"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="32" t="s">
         <v>373</v>
       </c>
     </row>
@@ -9276,19 +10019,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>262</v>
       </c>
@@ -9317,7 +10060,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>263</v>
       </c>
@@ -9346,7 +10089,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -9375,7 +10118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>264</v>
       </c>
@@ -9404,7 +10147,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -9433,7 +10176,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -9462,7 +10205,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -9491,7 +10234,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -9520,7 +10263,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>265</v>
       </c>
@@ -9549,7 +10292,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>266</v>
       </c>
@@ -9575,7 +10318,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>267</v>
       </c>
@@ -9601,7 +10344,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>268</v>
       </c>
@@ -9627,7 +10370,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>74</v>
       </c>
@@ -9653,7 +10396,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -9663,7 +10406,7 @@
       <c r="E14" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
@@ -9676,7 +10419,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>269</v>
       </c>
@@ -9686,7 +10429,7 @@
       <c r="E15" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="18" t="s">
         <v>21</v>
       </c>
       <c r="G15" t="s">
@@ -9699,7 +10442,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>270</v>
       </c>
@@ -9709,20 +10452,20 @@
       <c r="E16" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>358</v>
       </c>
       <c r="I16" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>271</v>
       </c>
@@ -9732,17 +10475,17 @@
       <c r="E17" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="18" t="s">
         <v>369</v>
       </c>
       <c r="I17" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>272</v>
       </c>
@@ -9752,17 +10495,17 @@
       <c r="E18" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="18" t="s">
         <v>101</v>
       </c>
       <c r="I18" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -9772,17 +10515,17 @@
       <c r="E19" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="18" t="s">
         <v>35</v>
       </c>
       <c r="I19" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -9792,17 +10535,17 @@
       <c r="E20" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="18" t="s">
         <v>373</v>
       </c>
       <c r="I20" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -9812,17 +10555,17 @@
       <c r="E21" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="18" t="s">
         <v>123</v>
       </c>
       <c r="I21" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -9832,62 +10575,62 @@
       <c r="E22" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="18" t="s">
         <v>412</v>
       </c>
       <c r="I22" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>273</v>
       </c>
       <c r="D23" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="18" t="s">
         <v>359</v>
       </c>
       <c r="I23" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>274</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="18" t="s">
         <v>156</v>
       </c>
       <c r="I24" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>275</v>
       </c>
       <c r="D25" t="s">
         <v>136</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="18" t="s">
         <v>288</v>
       </c>
       <c r="I25" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>276</v>
       </c>
@@ -9898,7 +10641,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>277</v>
       </c>
@@ -9909,7 +10652,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -9920,7 +10663,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>278</v>
       </c>
@@ -9931,7 +10674,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -9942,7 +10685,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>271</v>
       </c>
@@ -9953,7 +10696,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>272</v>
       </c>
@@ -9964,7 +10707,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -9972,7 +10715,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -9980,7 +10723,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -9988,7 +10731,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -9996,7 +10739,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>273</v>
       </c>
@@ -10004,7 +10747,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>274</v>
       </c>
@@ -10012,7 +10755,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>275</v>
       </c>
@@ -10020,7 +10763,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>276</v>
       </c>
@@ -10028,307 +10771,307 @@
         <v>373</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>375</v>
       </c>

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="645" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BDF4B9F-A944-4299-B4A4-A175A3495899}"/>
+  <xr:revisionPtr revIDLastSave="652" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3A0375F-9763-4D84-8668-0AD826C40505}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="431">
   <si>
     <t>Col 1</t>
   </si>
@@ -1328,6 +1328,9 @@
   </si>
   <si>
     <t>Col 102</t>
+  </si>
+  <si>
+    <t>59Z178-000-F</t>
   </si>
 </sst>
 </file>
@@ -1792,761 +1795,6 @@
   </cellStyles>
   <dxfs count="127">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -2977,6 +2225,720 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color auto="1"/>
@@ -2984,10 +2946,51 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -3004,148 +3007,148 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="124" dataDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G230">
     <sortCondition ref="A118:A230"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="122"/>
-    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="121"/>
-    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="119"/>
-    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="118"/>
-    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="117"/>
-    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="116"/>
-    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="115"/>
+    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="126" tableBorderDxfId="125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="126" dataDxfId="124" headerRowBorderDxfId="125" tableBorderDxfId="123">
   <autoFilter ref="A1:CX10" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}"/>
   <tableColumns count="102">
-    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="103"/>
-    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="101"/>
-    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="100"/>
-    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="99"/>
-    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="98"/>
-    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="97"/>
-    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="96"/>
-    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="95"/>
-    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="94"/>
-    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="93"/>
-    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="92"/>
-    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="91"/>
-    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="90"/>
-    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="89"/>
-    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="88"/>
-    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="87"/>
-    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="86"/>
-    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="85"/>
-    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="84"/>
-    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="83"/>
-    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="82"/>
-    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="81"/>
-    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="80"/>
-    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="79"/>
-    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="78"/>
-    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="77"/>
-    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="76"/>
-    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="75"/>
-    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="74"/>
-    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="73"/>
-    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="72"/>
-    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="71"/>
-    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="70"/>
-    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="69"/>
-    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="68"/>
-    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="67"/>
-    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="66"/>
-    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="65"/>
-    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="64"/>
-    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="63"/>
-    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="62"/>
-    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="61"/>
-    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="60"/>
-    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="59"/>
-    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="58"/>
-    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="57"/>
-    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="56"/>
-    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="55"/>
-    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="54"/>
-    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="53"/>
-    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="52"/>
-    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="51"/>
-    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="50"/>
-    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="49"/>
-    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="48"/>
-    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="47"/>
-    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="46"/>
-    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="45"/>
-    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="44"/>
-    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="43"/>
-    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="42"/>
-    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="41"/>
-    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="40"/>
-    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="39"/>
-    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="38"/>
-    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="37"/>
-    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="36"/>
-    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="35"/>
-    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="34"/>
-    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="33"/>
-    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="32"/>
-    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="31"/>
-    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="30"/>
-    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="29"/>
-    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="28"/>
-    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="27"/>
-    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="26"/>
-    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="25"/>
-    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="24"/>
-    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="23"/>
-    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="22"/>
-    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="21"/>
-    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="20"/>
-    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="19"/>
-    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="18"/>
-    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="17"/>
-    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="16"/>
-    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="15"/>
-    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="14"/>
-    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="13"/>
-    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="12"/>
-    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="11"/>
-    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="10"/>
-    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="9"/>
-    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="8"/>
-    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="7"/>
-    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="6"/>
-    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="5"/>
-    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="4"/>
-    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="3"/>
-    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="121"/>
+    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="119"/>
+    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="118"/>
+    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="117"/>
+    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="116"/>
+    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="114"/>
+    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="113"/>
+    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="112"/>
+    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="110"/>
+    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="109"/>
+    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="108"/>
+    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="107"/>
+    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="106"/>
+    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="105"/>
+    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="104"/>
+    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="103"/>
+    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="102"/>
+    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="101"/>
+    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="100"/>
+    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="99"/>
+    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="98"/>
+    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="97"/>
+    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="96"/>
+    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="95"/>
+    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="94"/>
+    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="93"/>
+    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="92"/>
+    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="91"/>
+    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="90"/>
+    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="89"/>
+    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="88"/>
+    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="87"/>
+    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="86"/>
+    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="85"/>
+    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="84"/>
+    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="83"/>
+    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="82"/>
+    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="81"/>
+    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="80"/>
+    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="79"/>
+    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="78"/>
+    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="77"/>
+    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="76"/>
+    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="75"/>
+    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="74"/>
+    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="73"/>
+    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="72"/>
+    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="71"/>
+    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="70"/>
+    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="69"/>
+    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="68"/>
+    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="67"/>
+    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="66"/>
+    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="65"/>
+    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="64"/>
+    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="63"/>
+    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="62"/>
+    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="61"/>
+    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="60"/>
+    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="59"/>
+    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="58"/>
+    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="57"/>
+    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="56"/>
+    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="55"/>
+    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="54"/>
+    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="53"/>
+    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="52"/>
+    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="51"/>
+    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="50"/>
+    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="49"/>
+    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="48"/>
+    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="47"/>
+    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="46"/>
+    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="45"/>
+    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="44"/>
+    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="43"/>
+    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="42"/>
+    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="41"/>
+    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="40"/>
+    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="39"/>
+    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="38"/>
+    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="37"/>
+    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="36"/>
+    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="35"/>
+    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="34"/>
+    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="33"/>
+    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="32"/>
+    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="31"/>
+    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="30"/>
+    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="29"/>
+    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="28"/>
+    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="27"/>
+    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="26"/>
+    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="25"/>
+    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="24"/>
+    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="23"/>
+    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="22"/>
+    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{98029534-FC1A-4188-9735-CF68321B5AC3}" name="Tabla3" displayName="Tabla3" ref="A1:I101" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{98029534-FC1A-4188-9735-CF68321B5AC3}" name="Tabla3" displayName="Tabla3" ref="A1:I101" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:I101" xr:uid="{98029534-FC1A-4188-9735-CF68321B5AC3}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5E4BDA70-F076-450B-A73E-034DF187DDD0}" name="FA1" dataDxfId="112"/>
-    <tableColumn id="2" xr3:uid="{728A5178-5E49-485C-811A-814C878280BD}" name="FA2" dataDxfId="111"/>
-    <tableColumn id="3" xr3:uid="{6512D9A4-ABA5-4A7F-B552-9FA02CBFBA15}" name="FA3" dataDxfId="110"/>
-    <tableColumn id="4" xr3:uid="{E3480F72-1A04-4419-A55B-8A371BCB83BB}" name="FA4" dataDxfId="109"/>
-    <tableColumn id="5" xr3:uid="{C5057181-6E4D-42CD-A672-89666A3A590F}" name="FA5" dataDxfId="108"/>
-    <tableColumn id="6" xr3:uid="{9E111813-83ED-4BC3-A5C2-2B23EDCBE045}" name="FA6" dataDxfId="107"/>
-    <tableColumn id="7" xr3:uid="{E3B443D2-6ABB-4DA9-85A3-23615366D11A}" name="FA7" dataDxfId="106"/>
-    <tableColumn id="8" xr3:uid="{9AD5DAC3-1F8A-44BE-8C81-D4E0724B6EED}" name="FA8" dataDxfId="105"/>
-    <tableColumn id="9" xr3:uid="{81F25ED4-3EA1-4016-930B-258B361297C7}" name="FA9" dataDxfId="104"/>
+    <tableColumn id="1" xr3:uid="{5E4BDA70-F076-450B-A73E-034DF187DDD0}" name="FA1" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{728A5178-5E49-485C-811A-814C878280BD}" name="FA2" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{6512D9A4-ABA5-4A7F-B552-9FA02CBFBA15}" name="FA3" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{E3480F72-1A04-4419-A55B-8A371BCB83BB}" name="FA4" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{C5057181-6E4D-42CD-A672-89666A3A590F}" name="FA5" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{9E111813-83ED-4BC3-A5C2-2B23EDCBE045}" name="FA6" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{E3B443D2-6ABB-4DA9-85A3-23615366D11A}" name="FA7" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{9AD5DAC3-1F8A-44BE-8C81-D4E0724B6EED}" name="FA8" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{81F25ED4-3EA1-4016-930B-258B361297C7}" name="FA9" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6748,8 +6751,8 @@
       <c r="C224" t="s">
         <v>158</v>
       </c>
-      <c r="D224" t="s">
-        <v>159</v>
+      <c r="D224" s="41" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
@@ -7757,7 +7760,7 @@
         <v>358</v>
       </c>
       <c r="AG5" s="41" t="s">
-        <v>159</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:102" x14ac:dyDescent="0.35">
@@ -8042,7 +8045,7 @@
         <v>365</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>159</v>
+        <v>430</v>
       </c>
       <c r="G10" s="41" t="s">
         <v>129</v>

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="652" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3A0375F-9763-4D84-8668-0AD826C40505}"/>
+  <xr:revisionPtr revIDLastSave="654" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFD0ED34-7814-4203-AC5A-E0ABCAD236EB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1340,7 +1340,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2787,24 +2787,24 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3029,7 +3029,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="116" dataDxfId="115" headerRowBorderDxfId="113" tableBorderDxfId="114">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113">
   <autoFilter ref="A1:CX10" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}"/>
   <tableColumns count="102">
     <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="112"/>
@@ -3475,19 +3475,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H233"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2088701244</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2088701390</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2088701610</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2088701746</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2088702198</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2088702199</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2088702200</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2088702201</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2088702202</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2088702203</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2088702204</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2088702205</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2088702206</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2088702207</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2088702221</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2088702318</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2088707042</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2098700024</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>2098700025</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2098700026</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2098700033</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2098700046</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2098700056</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2098700058</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2098700076</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2098700083</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>2098700108</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2098700143</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2098700154</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2098700177</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2098700189</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2098700245</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>2098700246</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>2098700256</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2098700289</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2098700290</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2098700293</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2098700296</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2098700301</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2098700302</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2098700304</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2098700305</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2098700306</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2098700307</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2098700309</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2098700315</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2098700316</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2098700320</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2098700322</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2098700353</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2098700355</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2098700356</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2098700357</v>
       </c>
@@ -4270,7 +4270,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2098700358</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2098700366</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2098700371</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2098700372</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2098700373</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2098700374</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2098700375</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2098700376</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2098700378</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>2098700379</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>2098700380</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>2098700404</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>2098700405</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2098700429</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>2098700432</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>2098700433</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>2098700434</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>2098700436</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>2098700437</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2098701682</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>2098706005</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>2098706008</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>2098706009</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2098706010</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2098706011</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2098706013</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2098706018</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2098706021</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2098706023</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>2098706024</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2098706025</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2098706026</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>2098706028</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>2098706031</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>2098706032</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2098706040</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>2098706041</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>2098706044</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>2098706072</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>2098706075</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>2098706076</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>2098706083</v>
       </c>
@@ -4861,7 +4861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>2098706084</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>2098706085</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>2098706087</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>2098706089</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>2099700009</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>2099700010</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2099700025</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2099700030</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>2099700041</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>2099700048</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>2099700049</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>2099700056</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>2099700057</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>2099700058</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>2099700059</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>2099706005</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>2154140069</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>2154140162</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>2154140207</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>2154140222</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>2154140224</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>2154140225</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>2154140229</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>2154140243</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2154140283</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2154140284</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>2154140285</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2154140287</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2154140289</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>2154140290</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>2154140291</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>2154140292</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2154140293</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2154140294</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2154140295</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>2154140318</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>2154140319</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>2154140335</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>2154140336</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>2154140345</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>2154140349</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>2154140596</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>2154150035</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>2154150089</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2154150163</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>2154150172</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>2154150197</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>2154150214</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>2154150215</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>2154150247</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>2154150250</v>
       </c>
@@ -5605,7 +5605,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>2154150301</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>2154150337</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>2154150341</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>2154150342</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>2154150343</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>2154150347</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>2154150348</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>2154150349</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>2154150350</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>2154150351</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>2154150357</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>2154150358</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>2154150366</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>2154150370</v>
       </c>
@@ -5810,7 +5810,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>2154150380</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>2154150391</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>2154150420</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>2154150447</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>2154150448</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>2154150455</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>2154150461</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>2154150497</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>2154150501</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>2154150509</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>2154150525</v>
       </c>
@@ -5970,7 +5970,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>2154150526</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="5">
         <v>2154150534</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>2154150554</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="5">
         <v>2154150557</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="5">
         <v>2154150560</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>2154150563</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>2154150581</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>2154150582</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>2154150588</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="5">
         <v>2154150591</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>2154150597</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>2154150603</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>2154150605</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="5">
         <v>2154150622</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="5">
         <v>2154150627</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>2154150633</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>2154150646</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>2154150648</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>2154150653</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>2154150669</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>2154150672</v>
       </c>
@@ -6291,7 +6291,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="5">
         <v>2154150677</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>2154150706</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>2154150707</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>2154150715</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="5">
         <v>2154150719</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="5">
         <v>2154150731</v>
       </c>
@@ -6378,7 +6378,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="5">
         <v>2154150765</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="5">
         <v>2154150767</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="5">
         <v>2154150769</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="5">
         <v>2154150788</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="5">
         <v>2154150813</v>
       </c>
@@ -6469,7 +6469,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="5">
         <v>2154150814</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>2154150822</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>2154150839</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>2154150840</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>2154150841</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="5">
         <v>2154150876</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="5">
         <v>2154150893</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="5">
         <v>2154150918</v>
       </c>
@@ -6587,7 +6587,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="5">
         <v>2154150921</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="5">
         <v>2154150922</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>2154150943</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>2154155136</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="5">
         <v>2154155149</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="5">
         <v>2154155150</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>2154160029</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>2154160030</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>2154160031</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>2154160032</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>2154160033</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>2154160034</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>2154160035</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>2154160036</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>2154160037</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>2154170049</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>2154170050</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>2154170052</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
     </row>
@@ -6871,88 +6871,88 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CX10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="39" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="39" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.54296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.54296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="14" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.5703125" style="39" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.5703125" style="39" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="39" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="39" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.54296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.54296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.54296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.54296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.453125" style="39" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="12" style="39" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.5703125" style="39" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="12.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="12.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.5703125" style="39" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="11.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="12.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12.85546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="12.7109375" style="39" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="12.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="60" max="63" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="12.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="65" max="66" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="11.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.1796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.54296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="12.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.54296875" style="39" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="11.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="12.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="60" max="63" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="65" max="66" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11.453125" style="39" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="12" style="39" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="71" max="72" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="12.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="74" max="77" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="79" max="80" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="11.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.1796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="71" max="72" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="74" max="77" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="79" max="80" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="11.453125" style="39" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="12" style="39" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="12.140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="85" max="86" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="12.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="88" max="91" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="12.28515625" style="39" bestFit="1" customWidth="1"/>
-    <col min="93" max="94" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="12.1796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="85" max="86" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="88" max="91" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
+    <col min="93" max="94" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.453125" style="39" bestFit="1" customWidth="1"/>
     <col min="96" max="96" width="12" style="39" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="12.140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="99" max="100" width="12.42578125" style="39" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="12.1796875" style="39" bestFit="1" customWidth="1"/>
+    <col min="99" max="100" width="12.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="13.453125" style="39" bestFit="1" customWidth="1"/>
     <col min="102" max="102" width="13" style="39" bestFit="1" customWidth="1"/>
-    <col min="103" max="16384" width="8.7109375" style="39"/>
+    <col min="103" max="16384" width="8.7265625" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102">
+    <row r="1" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:102">
+    <row r="2" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
         <v>205</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:102">
+    <row r="3" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A3" s="39" t="s">
         <v>252</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:102">
+    <row r="4" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A4" s="39" t="s">
         <v>254</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:102">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A5" s="39" t="s">
         <v>256</v>
       </c>
@@ -7721,37 +7721,34 @@
         <v>106</v>
       </c>
       <c r="X5" s="41" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="Y5" s="41" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="Z5" s="41" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="AA5" s="41" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="AB5" s="41" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="AC5" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD5" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="AE5" s="42" t="s">
+      <c r="AD5" s="42" t="s">
         <v>36</v>
       </c>
+      <c r="AE5" s="41" t="s">
+        <v>52</v>
+      </c>
       <c r="AF5" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG5" s="41" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:102">
+    <row r="6" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A6" s="39" t="s">
         <v>258</v>
       </c>
@@ -7843,7 +7840,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:102">
+    <row r="7" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A7" s="39" t="s">
         <v>261</v>
       </c>
@@ -7910,8 +7907,11 @@
       <c r="V7" s="42" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" spans="1:102">
+      <c r="W7" s="41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A8" s="39" t="s">
         <v>263</v>
       </c>
@@ -7972,7 +7972,7 @@
       <c r="T8" s="43"/>
       <c r="U8" s="43"/>
     </row>
-    <row r="9" spans="1:102">
+    <row r="9" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A9" s="39" t="s">
         <v>265</v>
       </c>
@@ -8016,7 +8016,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:102">
+    <row r="10" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A10" s="39" t="s">
         <v>267</v>
       </c>
@@ -8132,13 +8132,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AZ11"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="52" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="52" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>267</v>
       </c>
@@ -8296,7 +8296,7 @@
       <c r="AI2" s="36"/>
       <c r="AJ2" s="36"/>
     </row>
-    <row r="3" spans="1:52">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>205</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>2098700189</v>
       </c>
     </row>
-    <row r="4" spans="1:52">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>252</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>2154150715</v>
       </c>
     </row>
-    <row r="5" spans="1:52">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>254</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>2098706010</v>
       </c>
     </row>
-    <row r="6" spans="1:52">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>256</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>2088702198</v>
       </c>
     </row>
-    <row r="7" spans="1:52">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>258</v>
       </c>
@@ -8771,7 +8771,7 @@
         <v>2088701390</v>
       </c>
     </row>
-    <row r="8" spans="1:52">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>2088707042</v>
       </c>
     </row>
-    <row r="9" spans="1:52">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>263</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>2098700437</v>
       </c>
     </row>
-    <row r="10" spans="1:52">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>265</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>2154170049</v>
       </c>
     </row>
-    <row r="11" spans="1:52">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>377</v>
       </c>
@@ -8934,12 +8934,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>378</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>266</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>257</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>262</v>
       </c>
@@ -8971,7 +8971,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>383</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>257</v>
       </c>
@@ -8987,7 +8987,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>386</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>266</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>259</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>257</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>257</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>257</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>393</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>268</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>259</v>
       </c>
@@ -9067,17 +9067,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA531276-FCFB-48E9-A31C-F81A22563EEA}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>397</v>
       </c>
@@ -9106,7 +9106,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" thickBot="1">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>406</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="60">
+    <row r="3" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>415</v>
       </c>
@@ -9167,7 +9167,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="60">
+    <row r="4" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>416</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="60">
+    <row r="5" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>418</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="80.099999999999994">
+    <row r="6" spans="1:10" ht="80" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>419</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="60">
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>421</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="60">
+    <row r="8" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>422</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="60">
+    <row r="9" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>423</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="60">
+    <row r="10" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>25</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="60">
+    <row r="11" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A11" s="20"/>
       <c r="B11" s="19"/>
       <c r="C11" s="16" t="s">
@@ -9417,7 +9417,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="60">
+    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A12" s="20"/>
       <c r="B12" s="19"/>
       <c r="C12" s="16" t="s">
@@ -9445,7 +9445,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="60">
+    <row r="13" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A13" s="20"/>
       <c r="B13" s="19"/>
       <c r="C13" s="16" t="s">
@@ -9473,7 +9473,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="60">
+    <row r="14" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A14" s="20"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -9499,7 +9499,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="60">
+    <row r="15" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A15" s="20"/>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -9523,7 +9523,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="60">
+    <row r="16" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A16" s="20"/>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -9547,7 +9547,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="60">
+    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A17" s="20"/>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -9571,7 +9571,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="60">
+    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A18" s="20"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -9595,7 +9595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="60">
+    <row r="19" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A19" s="20"/>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -9619,7 +9619,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="60">
+    <row r="20" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A20" s="20"/>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -9643,7 +9643,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="60">
+    <row r="21" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A21" s="20"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -9667,7 +9667,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="60">
+    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A22" s="20"/>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -9689,7 +9689,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="60">
+    <row r="23" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A23" s="20"/>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -9711,7 +9711,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="60">
+    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A24" s="24"/>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -9733,7 +9733,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="60">
+    <row r="25" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A25" s="24"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -9755,7 +9755,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="60">
+    <row r="26" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A26" s="24"/>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -9775,7 +9775,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="60">
+    <row r="27" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A27" s="24"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -9795,7 +9795,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="60">
+    <row r="28" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A28" s="20"/>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -9813,7 +9813,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="60">
+    <row r="29" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A29" s="20"/>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -9831,7 +9831,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="60">
+    <row r="30" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A30" s="20"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
@@ -9849,7 +9849,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="60">
+    <row r="31" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A31" s="20"/>
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
@@ -9867,7 +9867,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="60">
+    <row r="32" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A32" s="20"/>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
@@ -9885,7 +9885,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="60">
+    <row r="33" spans="1:10" ht="40" x14ac:dyDescent="0.35">
       <c r="A33" s="20"/>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -9903,7 +9903,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="60">
+    <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.35">
       <c r="A34" s="20"/>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
@@ -9919,7 +9919,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="20"/>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
@@ -9932,7 +9932,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="20"/>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
@@ -9945,7 +9945,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="20"/>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
@@ -9958,7 +9958,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="20"/>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -9971,7 +9971,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="20"/>
       <c r="B39" s="19"/>
       <c r="C39" s="19"/>
@@ -9984,7 +9984,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" thickBot="1">
+    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="30"/>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
@@ -10008,16 +10008,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultColWidth="13.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>205</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>207</v>
       </c>
@@ -10133,7 +10133,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -10191,7 +10191,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -10220,7 +10220,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>208</v>
       </c>
@@ -10278,7 +10278,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>209</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>210</v>
       </c>
@@ -10330,7 +10330,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>211</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>212</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>213</v>
       </c>
@@ -10451,7 +10451,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>214</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>215</v>
       </c>
@@ -10491,7 +10491,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -10511,7 +10511,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>216</v>
       </c>
@@ -10588,7 +10588,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>217</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>218</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>219</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>220</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>221</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>214</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>215</v>
       </c>
@@ -10693,7 +10693,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -10709,7 +10709,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -10717,7 +10717,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -10725,7 +10725,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>216</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>217</v>
       </c>
@@ -10741,7 +10741,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>218</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>219</v>
       </c>
@@ -10757,307 +10757,307 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>251</v>
       </c>
@@ -11069,4 +11069,10 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{101ce67d-13f2-447a-bb65-0989b89dfdb4}" enabled="0" method="" siteId="{101ce67d-13f2-447a-bb65-0989b89dfdb4}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="654" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFD0ED34-7814-4203-AC5A-E0ABCAD236EB}"/>
+  <xr:revisionPtr revIDLastSave="657" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37950635-E1F0-4E91-AC26-E78B0610EA1E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1708,7 +1708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1792,6 +1792,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2066,775 +2067,6 @@
         </left>
         <right style="thin">
           <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
         </right>
         <top/>
         <bottom/>
@@ -2996,6 +2228,775 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -3010,130 +3011,130 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="126" dataDxfId="125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G230">
     <sortCondition ref="A118:A230"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="124"/>
-    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="123"/>
-    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="122"/>
-    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="121"/>
-    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="120"/>
-    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="119"/>
-    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="118"/>
-    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="117"/>
+    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="126" dataDxfId="124" headerRowBorderDxfId="125" tableBorderDxfId="123">
   <autoFilter ref="A1:CX10" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}"/>
   <tableColumns count="102">
-    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="112"/>
-    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="111"/>
-    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="110"/>
-    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="109"/>
-    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="108"/>
-    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="107"/>
-    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="106"/>
-    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="105"/>
-    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="104"/>
-    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="103"/>
-    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="102"/>
-    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="101"/>
-    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="100"/>
-    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="99"/>
-    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="98"/>
-    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="97"/>
-    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="96"/>
-    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="95"/>
-    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="94"/>
-    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="93"/>
-    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="92"/>
-    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="91"/>
-    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="90"/>
-    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="89"/>
-    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="88"/>
-    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="87"/>
-    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="86"/>
-    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="85"/>
-    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="84"/>
-    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="83"/>
-    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="82"/>
-    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="81"/>
-    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="80"/>
-    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="79"/>
-    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="78"/>
-    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="77"/>
-    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="76"/>
-    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="75"/>
-    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="74"/>
-    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="73"/>
-    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="72"/>
-    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="71"/>
-    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="70"/>
-    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="69"/>
-    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="68"/>
-    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="67"/>
-    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="66"/>
-    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="65"/>
-    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="64"/>
-    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="63"/>
-    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="62"/>
-    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="61"/>
-    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="60"/>
-    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="59"/>
-    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="58"/>
-    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="57"/>
-    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="56"/>
-    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="55"/>
-    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="54"/>
-    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="53"/>
-    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="52"/>
-    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="51"/>
-    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="50"/>
-    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="49"/>
-    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="48"/>
-    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="47"/>
-    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="46"/>
-    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="45"/>
-    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="44"/>
-    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="43"/>
-    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="42"/>
-    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="41"/>
-    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="40"/>
-    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="39"/>
-    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="38"/>
-    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="37"/>
-    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="36"/>
-    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="35"/>
-    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="34"/>
-    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="33"/>
-    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="32"/>
-    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="31"/>
-    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="30"/>
-    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="29"/>
-    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="28"/>
-    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="27"/>
-    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="26"/>
-    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="25"/>
-    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="24"/>
-    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="23"/>
-    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="22"/>
-    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="21"/>
-    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="20"/>
-    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="19"/>
-    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="18"/>
-    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="17"/>
-    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="16"/>
-    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="15"/>
-    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="14"/>
-    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="13"/>
-    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="12"/>
-    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="122"/>
+    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="121"/>
+    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="119"/>
+    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="118"/>
+    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="117"/>
+    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="116"/>
+    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="114"/>
+    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="113"/>
+    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="112"/>
+    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="110"/>
+    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="109"/>
+    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="108"/>
+    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="107"/>
+    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="106"/>
+    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="105"/>
+    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="104"/>
+    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="103"/>
+    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="102"/>
+    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="101"/>
+    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="100"/>
+    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="99"/>
+    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="98"/>
+    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="97"/>
+    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="96"/>
+    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="95"/>
+    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="94"/>
+    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="93"/>
+    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="92"/>
+    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="91"/>
+    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="90"/>
+    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="89"/>
+    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="88"/>
+    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="87"/>
+    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="86"/>
+    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="85"/>
+    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="84"/>
+    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="83"/>
+    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="82"/>
+    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="81"/>
+    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="80"/>
+    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="79"/>
+    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="78"/>
+    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="77"/>
+    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="76"/>
+    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="75"/>
+    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="74"/>
+    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="73"/>
+    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="72"/>
+    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="71"/>
+    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="70"/>
+    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="69"/>
+    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="68"/>
+    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="67"/>
+    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="66"/>
+    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="65"/>
+    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="64"/>
+    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="63"/>
+    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="62"/>
+    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="61"/>
+    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="60"/>
+    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="59"/>
+    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="58"/>
+    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="57"/>
+    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="56"/>
+    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="55"/>
+    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="54"/>
+    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="53"/>
+    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="52"/>
+    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="51"/>
+    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="50"/>
+    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="49"/>
+    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="48"/>
+    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="47"/>
+    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="46"/>
+    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="45"/>
+    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="44"/>
+    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="43"/>
+    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="42"/>
+    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="41"/>
+    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="40"/>
+    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="39"/>
+    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="38"/>
+    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="37"/>
+    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="36"/>
+    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="35"/>
+    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="34"/>
+    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="33"/>
+    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="32"/>
+    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="31"/>
+    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="30"/>
+    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="29"/>
+    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="28"/>
+    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="27"/>
+    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="26"/>
+    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="25"/>
+    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="24"/>
+    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="23"/>
+    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="22"/>
+    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8609,9 +8610,6 @@
       <c r="AB6" s="34">
         <v>2154150497</v>
       </c>
-      <c r="AC6" s="34">
-        <v>2088702198</v>
-      </c>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -8849,6 +8847,9 @@
       </c>
       <c r="Z8" s="34">
         <v>2088707042</v>
+      </c>
+      <c r="AA8" s="45">
+        <v>2088702198</v>
       </c>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.35">

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -8,17 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="657" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37950635-E1F0-4E91-AC26-E78B0610EA1E}"/>
+  <xr:revisionPtr revIDLastSave="666" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74FCDD26-9AD0-4CA6-AD38-558AF8678F39}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
     <sheet name="anotaciones" sheetId="4" r:id="rId4"/>
-    <sheet name="Datos del heri" sheetId="5" r:id="rId5"/>
-    <sheet name="Hoja oficial de busca" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="397">
   <si>
     <t>Col 1</t>
   </si>
@@ -1232,115 +1230,13 @@
   </si>
   <si>
     <t>se agrega 0256</t>
-  </si>
-  <si>
-    <t>LINEA 1</t>
-  </si>
-  <si>
-    <t>LINEA 2</t>
-  </si>
-  <si>
-    <t>LINEA 3</t>
-  </si>
-  <si>
-    <t>LINEA 4</t>
-  </si>
-  <si>
-    <t>LINEA 5</t>
-  </si>
-  <si>
-    <t>LINEA 6</t>
-  </si>
-  <si>
-    <t>LINEA 7</t>
-  </si>
-  <si>
-    <t>LINEA 8</t>
-  </si>
-  <si>
-    <t>LINEA 9</t>
-  </si>
-  <si>
-    <t>EOL 1</t>
-  </si>
-  <si>
-    <t>PERCHA 3</t>
-  </si>
-  <si>
-    <t>PERCHA 2</t>
-  </si>
-  <si>
-    <t>EOL 5</t>
-  </si>
-  <si>
-    <t>EOL 2</t>
-  </si>
-  <si>
-    <t>EOL 4</t>
-  </si>
-  <si>
-    <t>EOL 6</t>
-  </si>
-  <si>
-    <t>EOL 7</t>
-  </si>
-  <si>
-    <t>EOL 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59Z176-C01 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">59Z163-003 </t>
-  </si>
-  <si>
-    <t>2291859-2</t>
-  </si>
-  <si>
-    <t>59Z118-C00</t>
-  </si>
-  <si>
-    <t>59Z113-000</t>
-  </si>
-  <si>
-    <t>59K24K-1M4A4-F</t>
-  </si>
-  <si>
-    <t>59Z114-000</t>
-  </si>
-  <si>
-    <t>59Z113-000-1</t>
-  </si>
-  <si>
-    <t>59Z163-003-1</t>
-  </si>
-  <si>
-    <t>AMZ040-C00-D/E</t>
-  </si>
-  <si>
-    <t>59Z113-000N</t>
-  </si>
-  <si>
-    <t>AMZ010-C00-B+151-00785</t>
-  </si>
-  <si>
-    <t>59Z178-000</t>
-  </si>
-  <si>
-    <t>AMZ040-C00-D&amp;E</t>
-  </si>
-  <si>
-    <t>59Z153-C00-C+153216012</t>
-  </si>
-  <si>
-    <t>AMZ010-C00-B CLIP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1368,26 +1264,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1402,32 +1284,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CCEB"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="mediumGray">
-        <fgColor indexed="9"/>
-        <bgColor indexed="43"/>
       </patternFill>
     </fill>
     <fill>
@@ -1436,14 +1294,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="20">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1491,191 +1343,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1708,7 +1375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1719,88 +1386,767 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="127">
+  <dxfs count="116">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1810,263 +2156,23 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color auto="1"/>
         </left>
         <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color auto="1"/>
         </right>
         <top/>
         <bottom/>
@@ -2228,775 +2334,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -3011,148 +2348,130 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="115" dataDxfId="114">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G230">
     <sortCondition ref="A118:A230"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="113"/>
+    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="112"/>
+    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="111"/>
+    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="110"/>
+    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="109"/>
+    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="108"/>
+    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="107"/>
+    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="126" dataDxfId="124" headerRowBorderDxfId="125" tableBorderDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="105" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102">
   <autoFilter ref="A1:CX10" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}"/>
   <tableColumns count="102">
-    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="121"/>
-    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="120"/>
-    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="119"/>
-    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="118"/>
-    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="117"/>
-    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="116"/>
-    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="115"/>
-    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="114"/>
-    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="113"/>
-    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="112"/>
-    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="111"/>
-    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="110"/>
-    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="109"/>
-    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="108"/>
-    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="107"/>
-    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="106"/>
-    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="105"/>
-    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="104"/>
-    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="103"/>
-    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="102"/>
-    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="101"/>
-    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="100"/>
-    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="99"/>
-    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="98"/>
-    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="97"/>
-    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="96"/>
-    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="95"/>
-    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="94"/>
-    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="93"/>
-    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="92"/>
-    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="91"/>
-    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="90"/>
-    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="89"/>
-    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="88"/>
-    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="87"/>
-    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="86"/>
-    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="85"/>
-    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="84"/>
-    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="83"/>
-    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="82"/>
-    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="81"/>
-    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="80"/>
-    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="79"/>
-    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="78"/>
-    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="77"/>
-    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="76"/>
-    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="75"/>
-    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="74"/>
-    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="73"/>
-    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="72"/>
-    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="71"/>
-    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="70"/>
-    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="69"/>
-    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="68"/>
-    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="67"/>
-    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="66"/>
-    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="65"/>
-    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="64"/>
-    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="63"/>
-    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="62"/>
-    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="61"/>
-    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="60"/>
-    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="59"/>
-    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="58"/>
-    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="57"/>
-    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="56"/>
-    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="55"/>
-    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="54"/>
-    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="53"/>
-    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="52"/>
-    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="51"/>
-    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="50"/>
-    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="49"/>
-    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="48"/>
-    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="47"/>
-    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="46"/>
-    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="45"/>
-    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="44"/>
-    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="43"/>
-    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="42"/>
-    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="41"/>
-    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="40"/>
-    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="39"/>
-    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="38"/>
-    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="37"/>
-    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="36"/>
-    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="35"/>
-    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="34"/>
-    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="33"/>
-    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="32"/>
-    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="31"/>
-    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="30"/>
-    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="29"/>
-    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="28"/>
-    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="27"/>
-    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="26"/>
-    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="25"/>
-    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="24"/>
-    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="23"/>
-    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="22"/>
-    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="21"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{98029534-FC1A-4188-9735-CF68321B5AC3}" name="Tabla3" displayName="Tabla3" ref="A1:I101" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I101" xr:uid="{98029534-FC1A-4188-9735-CF68321B5AC3}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5E4BDA70-F076-450B-A73E-034DF187DDD0}" name="FA1" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{728A5178-5E49-485C-811A-814C878280BD}" name="FA2" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{6512D9A4-ABA5-4A7F-B552-9FA02CBFBA15}" name="FA3" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{E3480F72-1A04-4419-A55B-8A371BCB83BB}" name="FA4" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{C5057181-6E4D-42CD-A672-89666A3A590F}" name="FA5" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{9E111813-83ED-4BC3-A5C2-2B23EDCBE045}" name="FA6" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{E3B443D2-6ABB-4DA9-85A3-23615366D11A}" name="FA7" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{9AD5DAC3-1F8A-44BE-8C81-D4E0724B6EED}" name="FA8" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{81F25ED4-3EA1-4016-930B-258B361297C7}" name="FA9" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="101"/>
+    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="100"/>
+    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="99"/>
+    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="98"/>
+    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="97"/>
+    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="96"/>
+    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="95"/>
+    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="94"/>
+    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="93"/>
+    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="92"/>
+    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="91"/>
+    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="90"/>
+    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="89"/>
+    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="88"/>
+    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="87"/>
+    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="86"/>
+    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="85"/>
+    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="84"/>
+    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="83"/>
+    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="82"/>
+    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="81"/>
+    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="80"/>
+    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="79"/>
+    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="78"/>
+    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="77"/>
+    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="76"/>
+    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="75"/>
+    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="74"/>
+    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="73"/>
+    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="72"/>
+    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="71"/>
+    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="70"/>
+    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="69"/>
+    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="68"/>
+    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="67"/>
+    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="66"/>
+    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="65"/>
+    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="64"/>
+    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="63"/>
+    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="62"/>
+    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="61"/>
+    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="60"/>
+    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="59"/>
+    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="58"/>
+    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="57"/>
+    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="56"/>
+    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="55"/>
+    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="54"/>
+    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="53"/>
+    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="52"/>
+    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="51"/>
+    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="50"/>
+    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="49"/>
+    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="48"/>
+    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="47"/>
+    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="46"/>
+    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="45"/>
+    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="44"/>
+    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="43"/>
+    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="42"/>
+    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="41"/>
+    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="40"/>
+    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="39"/>
+    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="38"/>
+    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="37"/>
+    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="36"/>
+    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="35"/>
+    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="34"/>
+    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="33"/>
+    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="32"/>
+    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="31"/>
+    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="30"/>
+    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="29"/>
+    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="28"/>
+    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="27"/>
+    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="26"/>
+    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="25"/>
+    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="24"/>
+    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="23"/>
+    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="22"/>
+    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="21"/>
+    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="20"/>
+    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="19"/>
+    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="18"/>
+    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="17"/>
+    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="16"/>
+    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="15"/>
+    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="14"/>
+    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="13"/>
+    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="12"/>
+    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="11"/>
+    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="10"/>
+    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="9"/>
+    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="8"/>
+    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="7"/>
+    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="6"/>
+    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="5"/>
+    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="4"/>
+    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="3"/>
+    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="2"/>
+    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="1"/>
+    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3489,28 +2808,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -6755,7 +6074,7 @@
       <c r="C224" t="s">
         <v>50</v>
       </c>
-      <c r="D224" s="41" t="s">
+      <c r="D224" s="13" t="s">
         <v>107</v>
       </c>
     </row>
@@ -6874,1251 +6193,1249 @@
   <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.54296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.54296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.54296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.54296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.54296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.54296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12" style="39" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.1796875" style="39" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.54296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="12.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.54296875" style="39" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="11.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12.81640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="12.7265625" style="39" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="60" max="63" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="65" max="66" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="11.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="12" style="39" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.1796875" style="39" bestFit="1" customWidth="1"/>
-    <col min="71" max="72" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="74" max="77" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="79" max="80" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="11.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="12" style="39" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="12.1796875" style="39" bestFit="1" customWidth="1"/>
-    <col min="85" max="86" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="88" max="91" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="12.26953125" style="39" bestFit="1" customWidth="1"/>
-    <col min="93" max="94" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="12" style="39" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="12.1796875" style="39" bestFit="1" customWidth="1"/>
-    <col min="99" max="100" width="12.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.453125" style="39" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="13" style="39" bestFit="1" customWidth="1"/>
-    <col min="103" max="16384" width="8.7265625" style="39"/>
+    <col min="1" max="2" width="9.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12" style="11" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="12.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="11.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="12.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="12.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="60" max="63" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="65" max="66" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="12" style="11" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="71" max="72" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="74" max="77" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="79" max="80" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="11.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="12" style="11" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="12.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="85" max="86" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="88" max="91" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="12.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="93" max="94" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="12" style="11" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="12.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="99" max="100" width="12.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="13.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="13" style="11" bestFit="1" customWidth="1"/>
+    <col min="103" max="16384" width="8.7265625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="L1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="N1" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="P1" s="38" t="s">
+      <c r="P1" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="R1" s="38" t="s">
+      <c r="R1" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="S1" s="38" t="s">
+      <c r="S1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="T1" s="38" t="s">
+      <c r="T1" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="U1" s="38" t="s">
+      <c r="U1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="V1" s="38" t="s">
+      <c r="V1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="W1" s="38" t="s">
+      <c r="W1" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="X1" s="38" t="s">
+      <c r="X1" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="Y1" s="38" t="s">
+      <c r="Y1" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="Z1" s="38" t="s">
+      <c r="Z1" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="AA1" s="38" t="s">
+      <c r="AA1" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="AB1" s="38" t="s">
+      <c r="AB1" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="AC1" s="38" t="s">
+      <c r="AC1" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="AD1" s="38" t="s">
+      <c r="AD1" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="AE1" s="38" t="s">
+      <c r="AE1" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AF1" s="38" t="s">
+      <c r="AF1" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="AG1" s="38" t="s">
+      <c r="AG1" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="AH1" s="38" t="s">
+      <c r="AH1" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="AI1" s="38" t="s">
+      <c r="AI1" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="AJ1" s="38" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AK1" s="38" t="s">
+      <c r="AK1" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="AL1" s="38" t="s">
+      <c r="AL1" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="AM1" s="38" t="s">
+      <c r="AM1" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="AN1" s="38" t="s">
+      <c r="AN1" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="AO1" s="38" t="s">
+      <c r="AO1" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="AP1" s="38" t="s">
+      <c r="AP1" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="AQ1" s="38" t="s">
+      <c r="AQ1" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="AR1" s="38" t="s">
+      <c r="AR1" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="AS1" s="38" t="s">
+      <c r="AS1" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="AT1" s="38" t="s">
+      <c r="AT1" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="AU1" s="38" t="s">
+      <c r="AU1" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="AV1" s="38" t="s">
+      <c r="AV1" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="AW1" s="38" t="s">
+      <c r="AW1" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="AX1" s="38" t="s">
+      <c r="AX1" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="AY1" s="38" t="s">
+      <c r="AY1" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="AZ1" s="38" t="s">
+      <c r="AZ1" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="BA1" s="38" t="s">
+      <c r="BA1" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="BB1" s="38" t="s">
+      <c r="BB1" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="BC1" s="38" t="s">
+      <c r="BC1" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="BD1" s="38" t="s">
+      <c r="BD1" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="BE1" s="38" t="s">
+      <c r="BE1" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="BF1" s="38" t="s">
+      <c r="BF1" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="BG1" s="38" t="s">
+      <c r="BG1" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="BH1" s="38" t="s">
+      <c r="BH1" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="BI1" s="38" t="s">
+      <c r="BI1" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="BJ1" s="38" t="s">
+      <c r="BJ1" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="BK1" s="38" t="s">
+      <c r="BK1" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="BL1" s="38" t="s">
+      <c r="BL1" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="BM1" s="38" t="s">
+      <c r="BM1" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="BN1" s="38" t="s">
+      <c r="BN1" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="BO1" s="38" t="s">
+      <c r="BO1" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="BP1" s="38" t="s">
+      <c r="BP1" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="BQ1" s="38" t="s">
+      <c r="BQ1" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="BR1" s="38" t="s">
+      <c r="BR1" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="BS1" s="38" t="s">
+      <c r="BS1" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="BT1" s="38" t="s">
+      <c r="BT1" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="BU1" s="38" t="s">
+      <c r="BU1" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="BV1" s="38" t="s">
+      <c r="BV1" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="BW1" s="38" t="s">
+      <c r="BW1" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="BX1" s="38" t="s">
+      <c r="BX1" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="BY1" s="38" t="s">
+      <c r="BY1" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="BZ1" s="38" t="s">
+      <c r="BZ1" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="CA1" s="38" t="s">
+      <c r="CA1" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="CB1" s="38" t="s">
+      <c r="CB1" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="CC1" s="38" t="s">
+      <c r="CC1" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="CD1" s="38" t="s">
+      <c r="CD1" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="CE1" s="38" t="s">
+      <c r="CE1" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="CF1" s="38" t="s">
+      <c r="CF1" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="CG1" s="38" t="s">
+      <c r="CG1" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="CH1" s="38" t="s">
+      <c r="CH1" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="CI1" s="38" t="s">
+      <c r="CI1" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="CJ1" s="38" t="s">
+      <c r="CJ1" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="CK1" s="38" t="s">
+      <c r="CK1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="CL1" s="38" t="s">
+      <c r="CL1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="CM1" s="38" t="s">
+      <c r="CM1" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="CN1" s="38" t="s">
+      <c r="CN1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="CO1" s="38" t="s">
+      <c r="CO1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="CP1" s="38" t="s">
+      <c r="CP1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="CQ1" s="38" t="s">
+      <c r="CQ1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="CR1" s="38" t="s">
+      <c r="CR1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="CS1" s="38" t="s">
+      <c r="CS1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="CT1" s="38" t="s">
+      <c r="CT1" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="CU1" s="38" t="s">
+      <c r="CU1" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="CV1" s="38" t="s">
+      <c r="CV1" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="CW1" s="38" t="s">
+      <c r="CW1" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="CX1" s="38" t="s">
+      <c r="CX1" s="10" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="H2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="M2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="N2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="P2" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="Q2" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="R2" s="39" t="s">
+      <c r="R2" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="S2" s="39" t="s">
+      <c r="S2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="T2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="39" t="s">
+      <c r="U2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="39" t="s">
+      <c r="V2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="W2" s="39" t="s">
+      <c r="W2" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="X2" s="39" t="s">
+      <c r="X2" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="Y2" s="39" t="s">
+      <c r="Y2" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="Z2" s="39" t="s">
+      <c r="Z2" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="AA2" s="39" t="s">
+      <c r="AA2" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="AB2" s="39" t="s">
+      <c r="AB2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" s="39" t="s">
+      <c r="AC2" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="AD2" s="39" t="s">
+      <c r="AD2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AE2" s="39" t="s">
+      <c r="AE2" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="AF2" s="39" t="s">
+      <c r="AF2" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="AG2" s="39" t="s">
+      <c r="AG2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AH2" s="39" t="s">
+      <c r="AH2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AI2" s="39" t="s">
+      <c r="AI2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="AJ2" s="39" t="s">
+      <c r="AJ2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AK2" s="39" t="s">
+      <c r="AK2" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="AL2" s="39" t="s">
+      <c r="AL2" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="AM2" s="39" t="s">
+      <c r="AM2" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="AN2" s="39" t="s">
+      <c r="AN2" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="AO2" s="39" t="s">
+      <c r="AO2" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="AP2" s="39" t="s">
+      <c r="AP2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AQ2" s="39" t="s">
+      <c r="AQ2" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="AR2" s="39" t="s">
+      <c r="AR2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AS2" s="39" t="s">
+      <c r="AS2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="AT2" s="39" t="s">
+      <c r="AT2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="AU2" s="39" t="s">
+      <c r="AU2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AV2" s="39" t="s">
+      <c r="AV2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="AW2" s="39" t="s">
+      <c r="AW2" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="AX2" s="39" t="s">
+      <c r="AX2" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AY2" s="39" t="s">
+      <c r="AY2" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="AZ2" s="39" t="s">
+      <c r="AZ2" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="BA2" s="39" t="s">
+      <c r="BA2" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="BB2" s="39" t="s">
+      <c r="BB2" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="BC2" s="39" t="s">
+      <c r="BC2" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="BD2" s="39" t="s">
+      <c r="BD2" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="BE2" s="39" t="s">
+      <c r="BE2" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="BF2" s="39" t="s">
+      <c r="BF2" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="BG2" s="39" t="s">
+      <c r="BG2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="BH2" s="39" t="s">
+      <c r="BH2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="BI2" s="39" t="s">
+      <c r="BI2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="BJ2" s="39" t="s">
+      <c r="BJ2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="BK2" s="39" t="s">
+      <c r="BK2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="BL2" s="39" t="s">
+      <c r="BL2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="BM2" s="39" t="s">
+      <c r="BM2" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="BN2" s="39" t="s">
+      <c r="BN2" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="BO2" s="39" t="s">
+      <c r="BO2" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="BP2" s="39" t="s">
+      <c r="BP2" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="BQ2" s="39" t="s">
+      <c r="BQ2" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="BR2" s="39" t="s">
+      <c r="BR2" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="BS2" s="39" t="s">
+      <c r="BS2" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="BT2" s="39" t="s">
+      <c r="BT2" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="BU2" s="39" t="s">
+      <c r="BU2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="BV2" s="39" t="s">
+      <c r="BV2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="BW2" s="39" t="s">
+      <c r="BW2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="BX2" s="39" t="s">
+      <c r="BX2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="BY2" s="39" t="s">
+      <c r="BY2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="BZ2" s="39" t="s">
+      <c r="BZ2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="CA2" s="39" t="s">
+      <c r="CA2" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="CB2" s="39" t="s">
+      <c r="CB2" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="CC2" s="39" t="s">
+      <c r="CC2" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="CD2" s="39" t="s">
+      <c r="CD2" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="CE2" s="39" t="s">
+      <c r="CE2" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="CF2" s="39" t="s">
+      <c r="CF2" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="CG2" s="39" t="s">
+      <c r="CG2" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="CH2" s="39" t="s">
+      <c r="CH2" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="CI2" s="39" t="s">
+      <c r="CI2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="CJ2" s="39" t="s">
+      <c r="CJ2" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="CK2" s="39" t="s">
+      <c r="CK2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="CL2" s="39" t="s">
+      <c r="CL2" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="CM2" s="39" t="s">
+      <c r="CM2" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="CN2" s="39" t="s">
+      <c r="CN2" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="CO2" s="39" t="s">
+      <c r="CO2" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="CP2" s="39" t="s">
+      <c r="CP2" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="CQ2" s="39" t="s">
+      <c r="CQ2" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="CR2" s="39" t="s">
+      <c r="CR2" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="CS2" s="39" t="s">
+      <c r="CS2" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="CT2" s="39" t="s">
+      <c r="CT2" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="CU2" s="39" t="s">
+      <c r="CU2" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="CV2" s="39" t="s">
+      <c r="CV2" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="CW2" s="39" t="s">
+      <c r="CW2" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="CX2" s="40" t="s">
+      <c r="CX2" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="41" t="s">
+      <c r="K4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="41" t="s">
+      <c r="L4" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="M4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="41" t="s">
+      <c r="N4" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="42" t="s">
+      <c r="O4" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="41" t="s">
+      <c r="L5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="41" t="s">
+      <c r="M5" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="N5" s="41" t="s">
+      <c r="N5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="41" t="s">
+      <c r="O5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="41" t="s">
+      <c r="P5" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="Q5" s="41" t="s">
+      <c r="Q5" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="R5" s="41" t="s">
+      <c r="R5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="41" t="s">
+      <c r="S5" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T5" s="41" t="s">
+      <c r="T5" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="U5" s="41" t="s">
+      <c r="U5" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="V5" s="41" t="s">
+      <c r="V5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="W5" s="41" t="s">
+      <c r="W5" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="X5" s="41" t="s">
+      <c r="X5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="Y5" s="41" t="s">
+      <c r="Y5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="Z5" s="41" t="s">
+      <c r="Z5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="AA5" s="41" t="s">
+      <c r="AA5" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AB5" s="41" t="s">
+      <c r="AB5" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AC5" s="41" t="s">
+      <c r="AC5" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AD5" s="42" t="s">
+      <c r="AD5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AE5" s="41" t="s">
+      <c r="AE5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AF5" s="41" t="s">
+      <c r="AF5" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="41" t="s">
+      <c r="J6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="41" t="s">
+      <c r="K6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="41" t="s">
+      <c r="L6" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="41" t="s">
+      <c r="M6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="41" t="s">
+      <c r="N6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="O6" s="41" t="s">
+      <c r="O6" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="P6" s="41" t="s">
+      <c r="P6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="Q6" s="41" t="s">
+      <c r="Q6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="R6" s="41" t="s">
+      <c r="R6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="S6" s="41" t="s">
+      <c r="S6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="T6" s="41" t="s">
+      <c r="T6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="U6" s="41" t="s">
+      <c r="U6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="V6" s="41" t="s">
+      <c r="V6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="W6" s="41" t="s">
+      <c r="W6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="X6" s="41" t="s">
+      <c r="X6" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="Y6" s="41" t="s">
+      <c r="Y6" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="Z6" s="42" t="s">
+      <c r="Z6" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="AA6" s="42" t="s">
+      <c r="AA6" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AB6" s="41" t="s">
+      <c r="AB6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AC6" s="41" t="s">
+      <c r="AC6" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AD6" s="42" t="s">
+      <c r="AD6" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="41" t="s">
+      <c r="G7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="M7" s="42" t="s">
+      <c r="M7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="N7" s="42" t="s">
+      <c r="N7" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="O7" s="42" t="s">
+      <c r="O7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="42" t="s">
+      <c r="P7" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="Q7" s="42" t="s">
+      <c r="Q7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="R7" s="42" t="s">
+      <c r="R7" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="S7" s="42" t="s">
+      <c r="S7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="T7" s="42" t="s">
+      <c r="T7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="U7" s="42" t="s">
+      <c r="U7" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="V7" s="42" t="s">
+      <c r="V7" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="W7" s="41" t="s">
+      <c r="W7" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="T8" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="U8" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="V8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="W8" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="X8" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y8" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="Z8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA8" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB8" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD8" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF8" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="AG8" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH8" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:102" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C10" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D10" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E10" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H10" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I10" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="41" t="s">
+      <c r="K10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="L8" s="41" t="s">
+      <c r="L10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="M8" s="41" t="s">
+      <c r="M10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="N8" s="41" t="s">
+      <c r="N10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="41" t="s">
+      <c r="O10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="P8" s="42" t="s">
+      <c r="P10" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="Q8" s="42" t="s">
+      <c r="Q10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="R8" s="42" t="s">
+      <c r="R10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="S8" s="42" t="s">
+      <c r="S10" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-    </row>
-    <row r="9" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A9" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>266</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="J9" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="K9" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="L9" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="M9" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="N9" s="41" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:102" x14ac:dyDescent="0.35">
-      <c r="A10" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="M10" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="O10" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="P10" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q10" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="R10" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="S10" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="T10" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="U10" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="V10" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="W10" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="X10" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y10" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="Z10" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA10" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB10" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC10" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD10" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE10" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF10" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="AG10" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH10" s="41" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -8253,154 +7570,172 @@
       <c r="A2" t="s">
         <v>267</v>
       </c>
-      <c r="B2" s="34">
-        <v>2099700058</v>
-      </c>
-      <c r="C2" s="34">
-        <v>2099700059</v>
-      </c>
-      <c r="D2" s="34">
-        <v>2098700436</v>
-      </c>
-      <c r="E2" s="34">
-        <v>2098706085</v>
-      </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="36"/>
-      <c r="AF2" s="36"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="36"/>
-      <c r="AI2" s="36"/>
-      <c r="AJ2" s="36"/>
+      <c r="B2" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="L2" s="7">
+        <v>2154150788</v>
+      </c>
+      <c r="M2" s="7">
+        <v>2154160037</v>
+      </c>
+      <c r="N2" s="7">
+        <v>2098700437</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="J3" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="K3" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="M3" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N3" s="7">
         <v>2098700076</v>
       </c>
-      <c r="O3" s="34" t="s">
+      <c r="O3" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="P3" s="34" t="s">
+      <c r="P3" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="Q3" s="34" t="s">
+      <c r="Q3" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="R3" s="34" t="s">
+      <c r="R3" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="S3" s="34" t="s">
+      <c r="S3" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="T3" s="34" t="s">
+      <c r="T3" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="U3" s="34" t="s">
+      <c r="U3" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="V3" s="34" t="s">
+      <c r="V3" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="W3" s="34" t="s">
+      <c r="W3" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="X3" s="34" t="s">
+      <c r="X3" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="Y3" s="34" t="s">
+      <c r="Y3" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="Z3" s="34" t="s">
+      <c r="Z3" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="AA3" s="34" t="s">
+      <c r="AA3" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="AB3" s="34" t="s">
+      <c r="AB3" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="AC3" s="34" t="s">
+      <c r="AC3" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="AD3" s="34" t="s">
+      <c r="AD3" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="AE3" s="34">
+      <c r="AE3" s="7">
         <v>2088702318</v>
       </c>
-      <c r="AF3" s="34">
+      <c r="AF3" s="7">
         <v>2088706010</v>
       </c>
-      <c r="AG3" s="34">
+      <c r="AG3" s="7">
         <v>2098700429</v>
       </c>
-      <c r="AH3" s="34">
+      <c r="AH3" s="7">
         <v>2088701610</v>
       </c>
-      <c r="AI3" s="34">
+      <c r="AI3" s="7">
         <v>2098700189</v>
       </c>
     </row>
@@ -8408,55 +7743,55 @@
       <c r="A4" t="s">
         <v>252</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="N4" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="O4" s="34" t="s">
+      <c r="O4" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="7">
         <v>2154140336</v>
       </c>
       <c r="Q4">
         <v>2088701610</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="7">
         <v>2154150715</v>
       </c>
     </row>
@@ -8464,64 +7799,64 @@
       <c r="A5" t="s">
         <v>254</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="7">
         <v>2003020640</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="H5" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="J5" s="34" t="s">
+      <c r="J5" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="L5" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="M5" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="N5" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="O5" s="34" t="s">
+      <c r="O5" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="P5" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="7">
         <v>2098700305</v>
       </c>
-      <c r="R5" s="34">
+      <c r="R5" s="7">
         <v>2098706018</v>
       </c>
-      <c r="S5" s="34">
+      <c r="S5" s="7">
         <v>2098706011</v>
       </c>
-      <c r="T5" s="34">
+      <c r="T5" s="7">
         <v>2088702199</v>
       </c>
-      <c r="U5" s="34">
+      <c r="U5" s="7">
         <v>2098706010</v>
       </c>
     </row>
@@ -8529,85 +7864,85 @@
       <c r="A6" t="s">
         <v>256</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="J6" s="34" t="s">
+      <c r="J6" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="K6" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="L6" s="34" t="s">
+      <c r="L6" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="M6" s="34" t="s">
+      <c r="M6" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="N6" s="34" t="s">
+      <c r="N6" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="O6" s="34" t="s">
+      <c r="O6" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="P6" s="34" t="s">
+      <c r="P6" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="Q6" s="34" t="s">
+      <c r="Q6" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="R6" s="34">
+      <c r="R6" s="7">
         <v>2154160034</v>
       </c>
-      <c r="S6" s="34" t="s">
+      <c r="S6" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="T6" s="34">
+      <c r="T6" s="7">
         <v>2098700256</v>
       </c>
-      <c r="U6" s="34">
+      <c r="U6" s="7">
         <v>2098700304</v>
       </c>
-      <c r="V6" s="34" t="s">
+      <c r="V6" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="W6" s="34" t="s">
+      <c r="W6" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="X6" s="34">
+      <c r="X6" s="7">
         <v>2098700432</v>
       </c>
-      <c r="Y6" s="34">
+      <c r="Y6" s="7">
         <v>2098700433</v>
       </c>
-      <c r="Z6" s="34">
+      <c r="Z6" s="7">
         <v>2098700434</v>
       </c>
-      <c r="AA6" s="34">
+      <c r="AA6" s="7">
         <v>2154140324</v>
       </c>
-      <c r="AB6" s="34">
+      <c r="AB6" s="7">
         <v>2154150497</v>
       </c>
     </row>
@@ -8615,157 +7950,157 @@
       <c r="A7" t="s">
         <v>258</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="H7" s="34" t="s">
+      <c r="H7" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="J7" s="34" t="s">
+      <c r="J7" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="K7" s="34" t="s">
+      <c r="K7" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="L7" s="34" t="s">
+      <c r="L7" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="M7" s="34" t="s">
+      <c r="M7" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="N7" s="34" t="s">
+      <c r="N7" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="O7" s="34" t="s">
+      <c r="O7" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="P7" s="34" t="s">
+      <c r="P7" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="Q7" s="34" t="s">
+      <c r="Q7" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="R7" s="34" t="s">
+      <c r="R7" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="S7" s="34" t="s">
+      <c r="S7" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="T7" s="34" t="s">
+      <c r="T7" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="U7" s="34" t="s">
+      <c r="U7" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="V7" s="34" t="s">
+      <c r="V7" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="W7" s="34" t="s">
+      <c r="W7" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="X7" s="34" t="s">
+      <c r="X7" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="Y7" s="34" t="s">
+      <c r="Y7" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="Z7" s="34" t="s">
+      <c r="Z7" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="AA7" s="34" t="s">
+      <c r="AA7" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="AB7" s="34" t="s">
+      <c r="AB7" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="AC7" s="34" t="s">
+      <c r="AC7" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="AD7" s="34" t="s">
+      <c r="AD7" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="AE7" s="34" t="s">
+      <c r="AE7" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="AF7" s="34" t="s">
+      <c r="AF7" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="AG7" s="34" t="s">
+      <c r="AG7" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="AH7" s="34" t="s">
+      <c r="AH7" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="AI7" s="34" t="s">
+      <c r="AI7" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="AJ7" s="34" t="s">
+      <c r="AJ7" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="AK7" s="34">
+      <c r="AK7" s="7">
         <v>2098700379</v>
       </c>
-      <c r="AL7" s="34">
+      <c r="AL7" s="7">
         <v>2098700380</v>
       </c>
-      <c r="AM7" s="34">
+      <c r="AM7" s="7">
         <v>2098706024</v>
       </c>
-      <c r="AN7" s="34">
+      <c r="AN7" s="7">
         <v>2098706072</v>
       </c>
-      <c r="AO7" s="34">
+      <c r="AO7" s="7">
         <v>2098706075</v>
       </c>
-      <c r="AP7" s="34">
+      <c r="AP7" s="7">
         <v>2098706086</v>
       </c>
-      <c r="AQ7" s="34">
+      <c r="AQ7" s="7">
         <v>2098706087</v>
       </c>
-      <c r="AR7" s="34">
+      <c r="AR7" s="7">
         <v>2098706088</v>
       </c>
-      <c r="AS7" s="34">
+      <c r="AS7" s="7">
         <v>2098706089</v>
       </c>
-      <c r="AT7" s="34">
+      <c r="AT7" s="7">
         <v>2154140596</v>
       </c>
-      <c r="AU7" s="34">
+      <c r="AU7" s="7">
         <v>2098700434</v>
       </c>
-      <c r="AV7" s="34">
+      <c r="AV7" s="7">
         <v>2098700436</v>
       </c>
-      <c r="AW7" s="34">
+      <c r="AW7" s="7">
         <v>2098700256</v>
       </c>
-      <c r="AX7" s="34">
+      <c r="AX7" s="7">
         <v>2098700432</v>
       </c>
-      <c r="AY7" s="34">
+      <c r="AY7" s="7">
         <v>2098700433</v>
       </c>
-      <c r="AZ7" s="34">
+      <c r="AZ7" s="7">
         <v>2088701390</v>
       </c>
     </row>
@@ -8773,82 +8108,82 @@
       <c r="A8" t="s">
         <v>261</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="K8" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="L8" s="34" t="s">
+      <c r="L8" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M8" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="N8" s="34" t="s">
+      <c r="N8" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="O8" s="34" t="s">
+      <c r="O8" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="P8" s="34" t="s">
+      <c r="P8" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="Q8" s="34" t="s">
+      <c r="Q8" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="R8" s="34">
+      <c r="R8" s="7">
         <v>2154150840</v>
       </c>
-      <c r="S8" s="34">
+      <c r="S8" s="7">
         <v>2154150876</v>
       </c>
-      <c r="T8" s="34">
+      <c r="T8" s="7">
         <v>2154160037</v>
       </c>
-      <c r="U8" s="34">
+      <c r="U8" s="7">
         <v>2088702199</v>
       </c>
-      <c r="V8" s="34">
+      <c r="V8" s="7">
         <v>2088702200</v>
       </c>
-      <c r="W8" s="34">
+      <c r="W8" s="7">
         <v>2088702207</v>
       </c>
-      <c r="X8" s="34">
+      <c r="X8" s="7">
         <v>2088702221</v>
       </c>
-      <c r="Y8" s="34">
+      <c r="Y8" s="7">
         <v>2088702318</v>
       </c>
-      <c r="Z8" s="34">
+      <c r="Z8" s="7">
         <v>2088707042</v>
       </c>
-      <c r="AA8" s="45">
+      <c r="AA8" s="7">
         <v>2088702198</v>
       </c>
     </row>
@@ -8856,69 +8191,42 @@
       <c r="A9" t="s">
         <v>263</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>366</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>368</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>369</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>370</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>371</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>372</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>373</v>
-      </c>
-      <c r="J9" s="34" t="s">
-        <v>374</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>375</v>
-      </c>
-      <c r="L9" s="34">
-        <v>2154150788</v>
-      </c>
-      <c r="M9" s="34">
-        <v>2154160037</v>
-      </c>
-      <c r="N9" s="34">
-        <v>2098700437</v>
+      <c r="B9" s="7">
+        <v>2099700058</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2099700059</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2098700436</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2098706085</v>
       </c>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>265</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="7">
         <v>2099700057</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F10" s="34" t="s">
+      <c r="F10" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="7">
         <v>2154170049</v>
       </c>
     </row>
@@ -9065,2013 +8373,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA531276-FCFB-48E9-A31C-F81A22563EEA}">
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="80" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="J6" s="37" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A8" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>424</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A13" s="20"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="37" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A14" s="20"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A15" s="20"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A16" s="20"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A17" s="20"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>425</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="19"/>
-      <c r="I17" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="J17" s="37" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A18" s="20"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="19"/>
-      <c r="I18" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A19" s="20"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="19"/>
-      <c r="I19" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A20" s="20"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" s="19"/>
-      <c r="I20" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A21" s="20"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A22" s="20"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="18"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A23" s="20"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26" t="s">
-        <v>427</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="29" t="s">
-        <v>428</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A28" s="20"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A29" s="20"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A30" s="20"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A31" s="20"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A32" s="20"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="17" t="s">
-        <v>429</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="40" x14ac:dyDescent="0.35">
-      <c r="A33" s="20"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.35">
-      <c r="A34" s="20"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="29" t="s">
-        <v>430</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="20"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A36" s="20"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="20"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="17" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A38" s="20"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A39" s="20"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="30"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="32" t="s">
-        <v>99</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{723D49A2-FE28-4215-9CFB-3356189253E8}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F1" t="s">
-        <v>261</v>
-      </c>
-      <c r="G1" t="s">
-        <v>263</v>
-      </c>
-      <c r="H1" t="s">
-        <v>265</v>
-      </c>
-      <c r="I1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G2" t="s">
-        <v>264</v>
-      </c>
-      <c r="H2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>420</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" t="s">
-        <v>109</v>
-      </c>
-      <c r="I6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>209</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" t="s">
-        <v>74</v>
-      </c>
-      <c r="I11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>211</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" t="s">
-        <v>81</v>
-      </c>
-      <c r="I15" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>214</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="I17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>215</v>
-      </c>
-      <c r="D18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="I21" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>216</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>217</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>218</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>219</v>
-      </c>
-      <c r="D26" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>220</v>
-      </c>
-      <c r="D27" t="s">
-        <v>29</v>
-      </c>
-      <c r="I27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>221</v>
-      </c>
-      <c r="D29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I29" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>214</v>
-      </c>
-      <c r="D31" t="s">
-        <v>66</v>
-      </c>
-      <c r="I31" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>215</v>
-      </c>
-      <c r="D32" t="s">
-        <v>70</v>
-      </c>
-      <c r="I32" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>41</v>
-      </c>
-      <c r="I33" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>43</v>
-      </c>
-      <c r="I34" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="I35" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>216</v>
-      </c>
-      <c r="I37" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>217</v>
-      </c>
-      <c r="I38" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>218</v>
-      </c>
-      <c r="I39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>219</v>
-      </c>
-      <c r="I40" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>251</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="94" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{101ce67d-13f2-447a-bb65-0989b89dfdb4}" enabled="0" method="" siteId="{101ce67d-13f2-447a-bb65-0989b89dfdb4}" removed="1"/>

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="666" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74FCDD26-9AD0-4CA6-AD38-558AF8678F39}"/>
+  <xr:revisionPtr revIDLastSave="669" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E26667D5-0832-40C8-887F-36054051C079}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7859,6 +7859,9 @@
       <c r="U5" s="7">
         <v>2098706010</v>
       </c>
+      <c r="V5" s="7">
+        <v>2098706085</v>
+      </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A6" t="s">

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="669" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E26667D5-0832-40C8-887F-36054051C079}"/>
+  <xr:revisionPtr revIDLastSave="672" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27879EEC-15B9-4855-9437-2938C7A410D3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5667,7 +5667,7 @@
         <v>29</v>
       </c>
       <c r="D197" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
@@ -6896,30 +6896,27 @@
         <v>253</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="13" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7229,6 +7226,9 @@
       </c>
       <c r="W7" s="13" t="s">
         <v>13</v>
+      </c>
+      <c r="X7" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:102" x14ac:dyDescent="0.35">

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="672" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27879EEC-15B9-4855-9437-2938C7A410D3}"/>
+  <xr:revisionPtr revIDLastSave="676" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5350212-4C34-479D-A155-B301FFBA7916}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="397">
   <si>
     <t>Col 1</t>
   </si>
@@ -6131,7 +6131,13 @@
         <v>74</v>
       </c>
       <c r="D228" t="s">
+        <v>76</v>
+      </c>
+      <c r="E228" t="s">
         <v>108</v>
+      </c>
+      <c r="F228" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
@@ -6168,6 +6174,12 @@
         <v>74</v>
       </c>
       <c r="D230" t="s">
+        <v>76</v>
+      </c>
+      <c r="E230" t="s">
+        <v>108</v>
+      </c>
+      <c r="F230" t="s">
         <v>110</v>
       </c>
     </row>

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="676" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5350212-4C34-479D-A155-B301FFBA7916}"/>
+  <xr:revisionPtr revIDLastSave="691" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C5DAB6A-E55D-426B-9A54-4759ACBE3403}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="397">
   <si>
     <t>Col 1</t>
   </si>
@@ -7461,14 +7461,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:BD11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="52" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="56" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>267</v>
       </c>
@@ -7644,7 +7644,7 @@
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>205</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>2098700189</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>252</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>2154150715</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>254</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>2098706085</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>256</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>2154150497</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>258</v>
       </c>
@@ -8118,8 +8118,20 @@
       <c r="AZ7" s="7">
         <v>2088701390</v>
       </c>
-    </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="BA7" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="BB7" s="7">
+        <v>2098700305</v>
+      </c>
+      <c r="BC7" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="BD7" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -8202,7 +8214,7 @@
         <v>2088702198</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>263</v>
       </c>
@@ -8218,8 +8230,17 @@
       <c r="E9" s="7">
         <v>2098706085</v>
       </c>
-    </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="F9" s="7">
+        <v>2098700305</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="H9" s="7">
+        <v>2098706023</v>
+      </c>
+    </row>
+    <row r="10" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>265</v>
       </c>
@@ -8244,8 +8265,14 @@
       <c r="H10" s="7">
         <v>2154170049</v>
       </c>
-    </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="I10" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="J10" s="7">
+        <v>2098706023</v>
+      </c>
+    </row>
+    <row r="11" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>377</v>
       </c>

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="691" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C5DAB6A-E55D-426B-9A54-4759ACBE3403}"/>
+  <xr:revisionPtr revIDLastSave="695" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE774864-E229-4531-8942-6745D2548009}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -7076,6 +7076,9 @@
       <c r="AF5" s="13" t="s">
         <v>107</v>
       </c>
+      <c r="AG5" s="13" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:102" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
@@ -7235,9 +7238,6 @@
       </c>
       <c r="V7" s="14" t="s">
         <v>79</v>
-      </c>
-      <c r="W7" s="13" t="s">
-        <v>13</v>
       </c>
       <c r="X7" s="13" t="s">
         <v>65</v>
@@ -7960,6 +7960,9 @@
       <c r="AB6" s="7">
         <v>2154150497</v>
       </c>
+      <c r="AC6" s="7">
+        <v>2088702198</v>
+      </c>
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -8209,9 +8212,6 @@
       </c>
       <c r="Z8" s="7">
         <v>2088707042</v>
-      </c>
-      <c r="AA8" s="7">
-        <v>2088702198</v>
       </c>
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.35">

--- a/backend/data/AutomatedLines.xlsx
+++ b/backend/data/AutomatedLines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kochind-my.sharepoint.com/personal/moises_ramirez1_molex_com/Documents/aplicacionWeb/WebAppLineFinder/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="695" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE774864-E229-4531-8942-6745D2548009}"/>
+  <xr:revisionPtr revIDLastSave="700" documentId="13_ncr:1_{9CF0DDEB-C0A7-4BC9-A395-14399483BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06DF3213-F66E-4221-B35E-F89261121DC6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="397">
   <si>
     <t>Col 1</t>
   </si>
@@ -1295,7 +1295,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1371,11 +1371,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1404,780 +1417,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="116">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2334,6 +1580,775 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -2348,130 +2363,130 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H230" totalsRowShown="0" headerRowDxfId="115" dataDxfId="114">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CECFD1AD-A5A3-4ACE-B164-6FDF2FE2E95A}" name="Tabla1" displayName="Tabla1" ref="A1:H231" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G230">
     <sortCondition ref="A118:A230"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="113"/>
-    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="112"/>
-    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="111"/>
-    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="110"/>
-    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="109"/>
-    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="108"/>
-    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="107"/>
-    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="106"/>
+    <tableColumn id="1" xr3:uid="{529D4B34-4DA7-4DEA-82D6-FD2BD15A630D}" name="Col 1" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{CF499674-C182-4560-8B41-0E78F331A415}" name="Col 12" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{45F9BB40-479B-43A5-863C-7DF090960010}" name="Col 2" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{35AC3272-E32E-4533-B684-783CFFC3D97D}" name="Col 3" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{009711B2-C3BC-4C66-A5C8-5E23732ACEC7}" name="Col 4" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{DBF11C8B-3BA2-4B93-8B9D-B2B98230B63B}" name="Col 5" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{CC41153B-24E7-4D38-B346-9455226D8193}" name="Col 6" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{5BD831E8-A1B8-48E7-A7CD-262D4CCFAEA7}" name="Col 7" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="105" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}" name="Tabla2" displayName="Tabla2" ref="A1:CX10" totalsRowShown="0" headerRowDxfId="115" dataDxfId="113" headerRowBorderDxfId="114" tableBorderDxfId="112">
   <autoFilter ref="A1:CX10" xr:uid="{2551586D-350A-4849-A83B-B0EC7C8A022F}"/>
   <tableColumns count="102">
-    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="101"/>
-    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="100"/>
-    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="99"/>
-    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="98"/>
-    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="97"/>
-    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="96"/>
-    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="95"/>
-    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="94"/>
-    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="93"/>
-    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="92"/>
-    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="91"/>
-    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="90"/>
-    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="89"/>
-    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="88"/>
-    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="87"/>
-    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="86"/>
-    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="85"/>
-    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="84"/>
-    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="83"/>
-    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="82"/>
-    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="81"/>
-    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="80"/>
-    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="79"/>
-    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="78"/>
-    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="77"/>
-    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="76"/>
-    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="75"/>
-    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="74"/>
-    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="73"/>
-    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="72"/>
-    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="71"/>
-    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="70"/>
-    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="69"/>
-    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="68"/>
-    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="67"/>
-    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="66"/>
-    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="65"/>
-    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="64"/>
-    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="63"/>
-    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="62"/>
-    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="61"/>
-    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="60"/>
-    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="59"/>
-    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="58"/>
-    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="57"/>
-    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="56"/>
-    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="55"/>
-    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="54"/>
-    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="53"/>
-    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="52"/>
-    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="51"/>
-    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="50"/>
-    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="49"/>
-    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="48"/>
-    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="47"/>
-    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="46"/>
-    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="45"/>
-    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="44"/>
-    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="43"/>
-    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="42"/>
-    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="41"/>
-    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="40"/>
-    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="39"/>
-    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="38"/>
-    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="37"/>
-    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="36"/>
-    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="35"/>
-    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="34"/>
-    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="33"/>
-    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="32"/>
-    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="31"/>
-    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="30"/>
-    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="29"/>
-    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="28"/>
-    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="27"/>
-    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="26"/>
-    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="25"/>
-    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="24"/>
-    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="23"/>
-    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="22"/>
-    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="21"/>
-    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="20"/>
-    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="19"/>
-    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="18"/>
-    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="17"/>
-    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="16"/>
-    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="15"/>
-    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="14"/>
-    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="13"/>
-    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="12"/>
-    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="11"/>
-    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="10"/>
-    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="9"/>
-    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="8"/>
-    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="7"/>
-    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="6"/>
-    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="5"/>
-    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="4"/>
-    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="3"/>
-    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="2"/>
-    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="1"/>
-    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{515ED9AD-2115-402D-A669-A7974119647C}" name="Col 1" dataDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{4DD548BB-E585-4E18-BEB7-EC341F80577A}" name="Col 2" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{7D0A8B13-FDE9-43BD-B3DD-86603D1467E1}" name="Col 3" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{E6CD9477-D3FD-4183-B5C5-BA5552768D31}" name="Col 4" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{777800CA-01CA-4618-9E1F-B70C83DAEB01}" name="Col 5" dataDxfId="107"/>
+    <tableColumn id="6" xr3:uid="{E1C1DB5D-C27D-4C23-81E5-A9DF13A78A10}" name="Col 6" dataDxfId="106"/>
+    <tableColumn id="7" xr3:uid="{47605FA4-FEAF-4F2B-B1E3-14688AA5FE34}" name="Col 7" dataDxfId="105"/>
+    <tableColumn id="8" xr3:uid="{7FDAAA4E-ACAA-47E2-89B0-2A9A7E833B2E}" name="Col 8" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{E85CCC77-207F-4C47-B0CB-63A4D776409B}" name="Col 9" dataDxfId="103"/>
+    <tableColumn id="10" xr3:uid="{D9D92095-084F-4C5D-AF7C-C0C0A97EF0F3}" name="Col 10" dataDxfId="102"/>
+    <tableColumn id="11" xr3:uid="{A887ACE6-719B-47C5-ADC9-25C62650ADAD}" name="Col 11" dataDxfId="101"/>
+    <tableColumn id="12" xr3:uid="{30EEE989-5F4F-491A-B3DF-CCA8797CB49A}" name="Col 12" dataDxfId="100"/>
+    <tableColumn id="13" xr3:uid="{C9FCE6BD-5206-4F1D-8C10-D352EDF4BEC0}" name="Col 13" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{8E498461-0417-42FB-9E0F-D7DA3B1EA813}" name="Col 14" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{08EDDC5C-A7C3-4E14-A3D9-A2F9DB0F3BB1}" name="Col 15" dataDxfId="97"/>
+    <tableColumn id="16" xr3:uid="{AD9AE0D2-238B-424D-9B24-07BE7442E04F}" name="Col 16" dataDxfId="96"/>
+    <tableColumn id="17" xr3:uid="{2630B814-8919-4868-8DCE-1F2573BBC5B0}" name="Col 17" dataDxfId="95"/>
+    <tableColumn id="18" xr3:uid="{03CEE4E1-31A2-4724-A645-465CD2E045B9}" name="Col 18" dataDxfId="94"/>
+    <tableColumn id="19" xr3:uid="{36A35601-EAB7-4AB7-A614-7F8935936E6A}" name="Col 19" dataDxfId="93"/>
+    <tableColumn id="20" xr3:uid="{B07CF123-370C-4A46-A187-E8C3ECA28E61}" name="Col 20" dataDxfId="92"/>
+    <tableColumn id="21" xr3:uid="{3304A7B5-755F-4660-9241-F6EF4764F80B}" name="Col 21" dataDxfId="91"/>
+    <tableColumn id="22" xr3:uid="{4D5DD45C-EB23-4740-B7A8-ECA40874A151}" name="Col 22" dataDxfId="90"/>
+    <tableColumn id="23" xr3:uid="{76D5E9A0-768E-4FE8-83FA-EFEA599A0D33}" name="Col 23" dataDxfId="89"/>
+    <tableColumn id="24" xr3:uid="{02CD437C-7E42-4463-9013-107702C2B97F}" name="Col 24" dataDxfId="88"/>
+    <tableColumn id="25" xr3:uid="{DA504FA1-64F2-4573-B961-EE7FF96F946F}" name="Col 25" dataDxfId="87"/>
+    <tableColumn id="26" xr3:uid="{080C36A3-1279-43B3-9886-9F422C5195C2}" name="Col 26" dataDxfId="86"/>
+    <tableColumn id="27" xr3:uid="{F8545C41-9CAC-4EF7-BC34-973BAA53030F}" name="Col 27" dataDxfId="85"/>
+    <tableColumn id="28" xr3:uid="{75A7CF96-CABF-47B4-AB82-4FA4E53D81FB}" name="Col 28" dataDxfId="84"/>
+    <tableColumn id="29" xr3:uid="{8172C106-C018-4748-AA79-930FD33FB140}" name="Col 29" dataDxfId="83"/>
+    <tableColumn id="30" xr3:uid="{033ADE97-F3E4-4DA3-A83E-6147BDDBF1DF}" name="Col 30" dataDxfId="82"/>
+    <tableColumn id="31" xr3:uid="{F0C16803-0361-4D9C-9477-8426659282FD}" name="Col 31" dataDxfId="81"/>
+    <tableColumn id="32" xr3:uid="{910E3D06-6155-47EA-AF66-C13FA37B096F}" name="Col 32" dataDxfId="80"/>
+    <tableColumn id="33" xr3:uid="{BCA777C5-ED01-42A4-B051-4D833909B50A}" name="Col 33" dataDxfId="79"/>
+    <tableColumn id="34" xr3:uid="{7E1688F6-81EC-4DB2-816D-DCA58D556069}" name="Col 34" dataDxfId="78"/>
+    <tableColumn id="35" xr3:uid="{A7E1220E-D975-406D-948D-AD5ED3987172}" name="Col 35" dataDxfId="77"/>
+    <tableColumn id="36" xr3:uid="{CF7860C2-B04E-4553-8766-8D2252498B7D}" name="Col 36" dataDxfId="76"/>
+    <tableColumn id="37" xr3:uid="{FD24E187-D4BD-42A0-BC83-FCE2168C419B}" name="Col 37" dataDxfId="75"/>
+    <tableColumn id="38" xr3:uid="{78753972-0217-42B3-BB8C-339E763C03E9}" name="Col 38" dataDxfId="74"/>
+    <tableColumn id="39" xr3:uid="{49D7CC7C-78D2-499D-BF5B-204884E5C2CF}" name="Col 39" dataDxfId="73"/>
+    <tableColumn id="40" xr3:uid="{1664C61D-9B35-444D-856A-B5569FE7963E}" name="Col 40" dataDxfId="72"/>
+    <tableColumn id="41" xr3:uid="{1B7B38E0-6D44-4574-B87F-DB9CB0430C27}" name="Col 41" dataDxfId="71"/>
+    <tableColumn id="42" xr3:uid="{BE1E50E5-6C10-40D3-8355-68B05DE1AE9E}" name="Col 42" dataDxfId="70"/>
+    <tableColumn id="43" xr3:uid="{F25328DB-7EF2-4D70-B37F-946281B2D9BE}" name="Col 43" dataDxfId="69"/>
+    <tableColumn id="44" xr3:uid="{E46135CD-3747-49F8-A2C5-A9F3FA2A2F15}" name="Col 44" dataDxfId="68"/>
+    <tableColumn id="45" xr3:uid="{57F610BB-9B06-403D-A345-30B797486F2A}" name="Col 45" dataDxfId="67"/>
+    <tableColumn id="46" xr3:uid="{C35D3A15-1050-4B13-A99B-A8A95FD132F0}" name="Col 46" dataDxfId="66"/>
+    <tableColumn id="47" xr3:uid="{AE1CABF3-800E-4D52-B471-5594A79A1178}" name="Col 47" dataDxfId="65"/>
+    <tableColumn id="48" xr3:uid="{33E1DF5E-0C16-42C2-82D8-059D81FB61EF}" name="Col 48" dataDxfId="64"/>
+    <tableColumn id="49" xr3:uid="{110C8421-8763-4958-BCAB-586759DB96CF}" name="Col 49" dataDxfId="63"/>
+    <tableColumn id="50" xr3:uid="{EDE7C4F3-B0A2-4507-A2E3-7B8927DB17FF}" name="Col 50" dataDxfId="62"/>
+    <tableColumn id="51" xr3:uid="{03EA894E-E948-49F6-AC7B-1339E04F49F8}" name="Col 51" dataDxfId="61"/>
+    <tableColumn id="52" xr3:uid="{D95496CB-D58F-450B-B253-10F8B3315214}" name="Col 52" dataDxfId="60"/>
+    <tableColumn id="53" xr3:uid="{88D88FC3-D469-4679-AEED-690D6BDD1563}" name="Col 53" dataDxfId="59"/>
+    <tableColumn id="54" xr3:uid="{C9F66062-BDC8-403F-9A8B-3F6CB3D9346C}" name="Col 54" dataDxfId="58"/>
+    <tableColumn id="55" xr3:uid="{FED3AF10-DE5D-4DF5-A902-80BDE81919E0}" name="Col 55" dataDxfId="57"/>
+    <tableColumn id="56" xr3:uid="{2690A48E-9EA1-41A9-9B2B-3FDF4AFAD223}" name="Col 56" dataDxfId="56"/>
+    <tableColumn id="57" xr3:uid="{D2B40034-FF19-4BF8-B181-D750E9D1A041}" name="Col 57" dataDxfId="55"/>
+    <tableColumn id="58" xr3:uid="{1404B02A-959B-456B-98DA-FC7EDEC52138}" name="Col 58" dataDxfId="54"/>
+    <tableColumn id="59" xr3:uid="{43716E72-7E67-43AB-801F-D9C41994E8E6}" name="Col 59" dataDxfId="53"/>
+    <tableColumn id="60" xr3:uid="{528A42A9-5816-468C-B2A7-1081692BFFB7}" name="Col 60" dataDxfId="52"/>
+    <tableColumn id="61" xr3:uid="{C22372D4-C12E-4487-B962-F7E4F9836534}" name="Col 61" dataDxfId="51"/>
+    <tableColumn id="62" xr3:uid="{28D784EB-BF9D-429D-A5E8-D4329D65201A}" name="Col 62" dataDxfId="50"/>
+    <tableColumn id="63" xr3:uid="{8FA59AD3-BDFE-41ED-B471-076755538EAC}" name="Col 63" dataDxfId="49"/>
+    <tableColumn id="64" xr3:uid="{AF2A2D6D-4529-48ED-A9D9-25E566D21C68}" name="Col 64" dataDxfId="48"/>
+    <tableColumn id="65" xr3:uid="{83FBFC62-D5D2-4A46-9149-ED1B85FCBC17}" name="Col 65" dataDxfId="47"/>
+    <tableColumn id="66" xr3:uid="{02788A26-6698-4416-BC3D-C7DEF6B5B6B4}" name="Col 66" dataDxfId="46"/>
+    <tableColumn id="67" xr3:uid="{41235750-E626-4FED-9EA1-42BD8F578D29}" name="Col 67" dataDxfId="45"/>
+    <tableColumn id="68" xr3:uid="{2DF4E672-C2E5-49F4-8FE8-8F563C2E74A0}" name="Col 68" dataDxfId="44"/>
+    <tableColumn id="69" xr3:uid="{45CBB860-0CF4-430A-9D41-DEDC6D4435AD}" name="Col 69" dataDxfId="43"/>
+    <tableColumn id="70" xr3:uid="{FA638996-E077-437A-AEC9-761FB83B74A8}" name="Col 70" dataDxfId="42"/>
+    <tableColumn id="71" xr3:uid="{EC0D9C98-7817-4D2F-BBF6-93E2737118F4}" name="Col 71" dataDxfId="41"/>
+    <tableColumn id="72" xr3:uid="{DA4E9A3B-364C-4787-922E-47CFDD1D23B8}" name="Col 72" dataDxfId="40"/>
+    <tableColumn id="73" xr3:uid="{6686A209-D8A9-4E28-B764-82A2AD26DD72}" name="Col 73" dataDxfId="39"/>
+    <tableColumn id="74" xr3:uid="{A97309D3-1AEB-4303-9733-6B03D92DC450}" name="Col 74" dataDxfId="38"/>
+    <tableColumn id="75" xr3:uid="{BC424F0B-0CBC-46CA-9D43-49C5D4D12084}" name="Col 75" dataDxfId="37"/>
+    <tableColumn id="76" xr3:uid="{40FFB765-2CF6-4F36-8FB4-144ABFB67BD2}" name="Col 76" dataDxfId="36"/>
+    <tableColumn id="77" xr3:uid="{4739DE29-84E8-475D-818B-7049D885DC76}" name="Col 77" dataDxfId="35"/>
+    <tableColumn id="78" xr3:uid="{7F3F3930-1E9D-45AE-ACAD-B8835C519E36}" name="Col 78" dataDxfId="34"/>
+    <tableColumn id="79" xr3:uid="{C5F83322-36B9-471A-BCD8-8CCE63CE4CC9}" name="Col 79" dataDxfId="33"/>
+    <tableColumn id="80" xr3:uid="{0AE29E9F-22FE-4103-85D1-3ED27F1C21B0}" name="Col 80" dataDxfId="32"/>
+    <tableColumn id="81" xr3:uid="{B86D5E9E-38C1-40FD-A0A0-65F8B0627EFC}" name="Col 81" dataDxfId="31"/>
+    <tableColumn id="82" xr3:uid="{DCB2BC17-B8D5-4EE9-8D35-E9333DA85146}" name="Col 82" dataDxfId="30"/>
+    <tableColumn id="83" xr3:uid="{CE75F411-AF0C-4F05-8569-EC5890BBE475}" name="Col 83" dataDxfId="29"/>
+    <tableColumn id="84" xr3:uid="{5C42F387-A9E2-4DC0-BE8D-DC5C590D89D3}" name="Col 84" dataDxfId="28"/>
+    <tableColumn id="85" xr3:uid="{29C9A99E-A5B0-40A4-AE16-4E91D03A520F}" name="Col 85" dataDxfId="27"/>
+    <tableColumn id="86" xr3:uid="{DD1E90CC-744B-40C6-AF6B-C27D715B7028}" name="Col 86" dataDxfId="26"/>
+    <tableColumn id="87" xr3:uid="{B3FCB1DB-E744-4C30-A492-F70B45EB645F}" name="Col 87" dataDxfId="25"/>
+    <tableColumn id="88" xr3:uid="{86C3CE83-2701-497E-BAAB-BD6E5BE9D25F}" name="Col 88" dataDxfId="24"/>
+    <tableColumn id="89" xr3:uid="{54E1ABF7-C9B0-4DF3-936F-B06C61F4D1AF}" name="Col 89" dataDxfId="23"/>
+    <tableColumn id="90" xr3:uid="{2F8BC889-9706-413E-8B0A-8CB66FA56EE6}" name="Col 90" dataDxfId="22"/>
+    <tableColumn id="91" xr3:uid="{744DB11E-AB2C-41E5-846F-71432CBD81E7}" name="Col 91" dataDxfId="21"/>
+    <tableColumn id="92" xr3:uid="{E9F7DAA5-0516-44B3-A6A4-DA2211281BE1}" name="Col 92" dataDxfId="20"/>
+    <tableColumn id="93" xr3:uid="{9889A6EF-A74B-423D-BDF9-A39020570EAB}" name="Col 93" dataDxfId="19"/>
+    <tableColumn id="94" xr3:uid="{540A74DA-B0E2-44FE-AE26-A7CFE9D5167A}" name="Col 94" dataDxfId="18"/>
+    <tableColumn id="95" xr3:uid="{64B11637-83D7-4E06-A33A-59DA71A9C1B1}" name="Col 95" dataDxfId="17"/>
+    <tableColumn id="96" xr3:uid="{6A83FE22-16AD-4DB7-84DC-DB55D967851C}" name="Col 96" dataDxfId="16"/>
+    <tableColumn id="97" xr3:uid="{C3E53C3E-EF93-4DF5-89F3-4B5535A4B63F}" name="Col 97" dataDxfId="15"/>
+    <tableColumn id="98" xr3:uid="{DB7106AA-4F3A-492C-B1E6-6605F7A5AFFA}" name="Col 98" dataDxfId="14"/>
+    <tableColumn id="99" xr3:uid="{092A0299-48D1-4BF5-8176-E19BBB43288F}" name="Col 99" dataDxfId="13"/>
+    <tableColumn id="100" xr3:uid="{A85ACC83-4078-4DD2-812A-10CF55A6E678}" name="Col 100" dataDxfId="12"/>
+    <tableColumn id="101" xr3:uid="{9DF18404-F344-4718-98A8-ED34BE772269}" name="Col 101" dataDxfId="11"/>
+    <tableColumn id="102" xr3:uid="{EC091E45-98D0-445E-8564-9D521EDB27CE}" name="Col 102" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6078,7 +6093,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>2154160035</v>
       </c>
@@ -6092,7 +6107,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>2154160036</v>
       </c>
@@ -6106,7 +6121,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>2154160037</v>
       </c>
@@ -6120,7 +6135,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>2154170049</v>
       </c>
@@ -6140,7 +6155,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>2154170050</v>
       </c>
@@ -6163,7 +6178,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>2154170052</v>
       </c>
@@ -6183,7 +6198,25 @@
         <v>110</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>2267110028</v>
+      </c>
+      <c r="B231" t="s">
+        <v>8</v>
+      </c>
+      <c r="C231" t="s">
+        <v>23</v>
+      </c>
+      <c r="D231" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E231" s="17"/>
+      <c r="F231" s="17"/>
+      <c r="G231" s="17"/>
+      <c r="H231" s="17"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
     </row>
@@ -8213,6 +8246,9 @@
       <c r="Z8" s="7">
         <v>2088707042</v>
       </c>
+      <c r="AA8" s="16">
+        <v>2267110028</v>
+      </c>
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
